--- a/Deliverables/SM_Bottom Board/_BOM/Supplier BOM_Bottom (20 Boards).xlsx
+++ b/Deliverables/SM_Bottom Board/_BOM/Supplier BOM_Bottom (20 Boards).xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Bottom Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Bottom Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="215">
   <si>
     <t>Component list</t>
   </si>
@@ -475,27 +475,12 @@
     <t>Item Type</t>
   </si>
   <si>
-    <t>Alternate Part Number</t>
-  </si>
-  <si>
     <t>LCSC Part Number</t>
   </si>
   <si>
     <t>Quantity (20 Boards)</t>
   </si>
   <si>
-    <t>MOQ (20 Boards)</t>
-  </si>
-  <si>
-    <t>Links</t>
-  </si>
-  <si>
-    <t>Unit Cost (20 Boards)</t>
-  </si>
-  <si>
-    <t>Total Cost (20 Boards)</t>
-  </si>
-  <si>
     <t>Remarks</t>
   </si>
   <si>
@@ -505,9 +490,6 @@
     <t>C69335</t>
   </si>
   <si>
-    <t>LCSC</t>
-  </si>
-  <si>
     <t>C1591</t>
   </si>
   <si>
@@ -544,9 +526,6 @@
     <t>C307770</t>
   </si>
   <si>
-    <t>Mouser</t>
-  </si>
-  <si>
     <t>C515365</t>
   </si>
   <si>
@@ -556,9 +535,6 @@
     <t>C401111</t>
   </si>
   <si>
-    <t>Digikey</t>
-  </si>
-  <si>
     <t>C94515</t>
   </si>
   <si>
@@ -607,9 +583,6 @@
     <t>C123083</t>
   </si>
   <si>
-    <t>UTSource</t>
-  </si>
-  <si>
     <t>C100024</t>
   </si>
   <si>
@@ -617,12 +590,6 @@
   </si>
   <si>
     <t>32.768KHz</t>
-  </si>
-  <si>
-    <t>Total Cost</t>
-  </si>
-  <si>
-    <t>Cost per Board</t>
   </si>
   <si>
     <t>D1</t>
@@ -676,9 +643,6 @@
     <t>Multiple options added for MCU</t>
   </si>
   <si>
-    <t>STM32F407VGT6, STM32F407VET6</t>
-  </si>
-  <si>
     <t>1uF 16V -55℃~+125℃ 11Ω ±10% CASE-A_3216</t>
   </si>
   <si>
@@ -727,11 +691,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -855,22 +819,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
@@ -889,13 +837,6 @@
       <strike/>
       <sz val="9"/>
       <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1184,11 +1125,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1345,58 +1285,37 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1405,13 +1324,7 @@
     <xf numFmtId="0" fontId="17" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1424,8 +1337,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1451,13 +1363,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>17</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>1905000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -1467,7 +1379,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1765,26 +1677,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M44"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.1796875" style="25" customWidth="1"/>
+    <col min="3" max="3" width="18.7265625" style="25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="33.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.85546875" customWidth="1"/>
-    <col min="14" max="15" width="19.140625" customWidth="1"/>
-    <col min="16" max="18" width="29.42578125" customWidth="1"/>
-    <col min="20" max="20" width="18.28515625" customWidth="1"/>
+    <col min="6" max="6" width="26.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.453125" customWidth="1"/>
+    <col min="10" max="10" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.81640625" customWidth="1"/>
+    <col min="13" max="13" width="29.453125" customWidth="1"/>
+    <col min="15" max="15" width="18.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1794,17 +1705,12 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-    </row>
-    <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+    </row>
+    <row r="2" spans="1:13" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="46"/>
@@ -1818,17 +1724,12 @@
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
+      <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="43"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M2" s="43"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="47"/>
@@ -1842,17 +1743,12 @@
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
       <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
+      <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="83"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M3" s="74"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="47"/>
@@ -1866,17 +1762,12 @@
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
       <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
+      <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="59"/>
-      <c r="R4" s="84"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M4" s="75"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="47"/>
@@ -1890,17 +1781,12 @@
       <c r="G5" s="14"/>
       <c r="H5" s="5"/>
       <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
+      <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="59"/>
-      <c r="R5" s="84"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M5" s="75"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="48"/>
@@ -1910,17 +1796,12 @@
       <c r="G6" s="14"/>
       <c r="H6" s="5"/>
       <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
+      <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="84"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M6" s="75"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="49"/>
@@ -1930,17 +1811,12 @@
       <c r="G7" s="17"/>
       <c r="H7" s="7"/>
       <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
+      <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="84"/>
-    </row>
-    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M7" s="75"/>
+    </row>
+    <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="50"/>
@@ -1950,17 +1826,12 @@
       <c r="G8" s="17"/>
       <c r="H8" s="7"/>
       <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
+      <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="84"/>
-    </row>
-    <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="75"/>
+    </row>
+    <row r="9" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
@@ -1986,35 +1857,20 @@
       <c r="I9" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="J9" s="29" t="s">
+      <c r="J9" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="L9" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="K9" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="L9" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="M9" s="29" t="s">
+      <c r="M9" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="N9" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="O9" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="P9" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q9" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="R9" s="31" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
       <c r="B10" s="53">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -2039,37 +1895,21 @@
         <v>103</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="J10" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="K10" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="J10" s="38" t="s">
         <v>120</v>
       </c>
+      <c r="K10" s="37">
+        <v>1</v>
+      </c>
       <c r="L10" s="37">
-        <v>1</v>
-      </c>
-      <c r="M10" s="37">
-        <f>L10*20</f>
+        <f>K10*20</f>
         <v>20</v>
       </c>
-      <c r="N10" s="37">
-        <v>40</v>
-      </c>
-      <c r="O10" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P10" s="37">
-        <v>1.9199999999999998E-2</v>
-      </c>
-      <c r="Q10" s="41">
-        <f>P10*N10</f>
-        <v>0.7679999999999999</v>
-      </c>
-      <c r="R10" s="41"/>
-    </row>
-    <row r="11" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M10" s="41"/>
+    </row>
+    <row r="11" spans="1:13" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
         <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
@@ -2079,7 +1919,7 @@
         <v>134</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="E11" s="40" t="s">
         <v>42</v>
@@ -2094,39 +1934,23 @@
         <v>103</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="J11" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="K11" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="J11" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="L11" s="73">
+      <c r="K11" s="66">
         <v>18</v>
       </c>
-      <c r="M11" s="39">
-        <f>L11*20</f>
+      <c r="L11" s="39">
+        <f>K11*20</f>
         <v>360</v>
       </c>
-      <c r="N11" s="39">
-        <v>400</v>
-      </c>
-      <c r="O11" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="P11" s="39">
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q11" s="42">
-        <f t="shared" ref="Q11:Q42" si="1">P11*N11</f>
-        <v>0.55999999999999994</v>
-      </c>
-      <c r="R11" s="76" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M11" s="69" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
       <c r="B12" s="53">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -2139,49 +1963,33 @@
         <v>12</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F12" s="37" t="s">
         <v>145</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H12" s="37" t="s">
         <v>104</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="J12" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="K12" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="J12" s="38" t="s">
         <v>122</v>
       </c>
+      <c r="K12" s="37">
+        <v>1</v>
+      </c>
       <c r="L12" s="37">
-        <v>1</v>
-      </c>
-      <c r="M12" s="37">
-        <f t="shared" ref="M12:M30" si="2">L12*20</f>
+        <f t="shared" ref="L12:L30" si="1">K12*20</f>
         <v>20</v>
       </c>
-      <c r="N12" s="37">
-        <v>25</v>
-      </c>
-      <c r="O12" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P12" s="37">
-        <v>6.1499999999999999E-2</v>
-      </c>
-      <c r="Q12" s="41">
-        <f t="shared" si="1"/>
-        <v>1.5375000000000001</v>
-      </c>
-      <c r="R12" s="69"/>
-    </row>
-    <row r="13" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M12" s="62"/>
+    </row>
+    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="53">
         <f t="shared" si="0"/>
@@ -2208,35 +2016,19 @@
       <c r="I13" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="J13" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="K13" s="40" t="s">
+      <c r="J13" s="40" t="s">
         <v>123</v>
       </c>
+      <c r="K13" s="39">
+        <v>2</v>
+      </c>
       <c r="L13" s="39">
-        <v>2</v>
-      </c>
-      <c r="M13" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N13" s="39">
-        <v>50</v>
-      </c>
-      <c r="O13" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="P13" s="39">
-        <v>5.0099999999999999E-2</v>
-      </c>
-      <c r="Q13" s="42">
-        <f t="shared" si="1"/>
-        <v>2.5049999999999999</v>
-      </c>
-      <c r="R13" s="42"/>
-    </row>
-    <row r="14" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M13" s="42"/>
+    </row>
+    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
       <c r="B14" s="53">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -2261,37 +2053,21 @@
         <v>106</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="K14" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="J14" s="38" t="s">
         <v>124</v>
       </c>
+      <c r="K14" s="37">
+        <v>2</v>
+      </c>
       <c r="L14" s="37">
-        <v>2</v>
-      </c>
-      <c r="M14" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N14" s="37">
-        <v>100</v>
-      </c>
-      <c r="O14" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P14" s="37">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="Q14" s="41">
-        <f t="shared" si="1"/>
-        <v>0.33999999999999997</v>
-      </c>
-      <c r="R14" s="41"/>
-    </row>
-    <row r="15" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M14" s="41"/>
+    </row>
+    <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
       <c r="B15" s="53">
         <f t="shared" si="0"/>
@@ -2304,49 +2080,33 @@
         <v>15</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F15" s="39" t="s">
         <v>68</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="H15" s="39" t="s">
         <v>110</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="J15" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="K15" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="J15" s="40" t="s">
         <v>125</v>
       </c>
+      <c r="K15" s="39">
+        <v>2</v>
+      </c>
       <c r="L15" s="39">
-        <v>2</v>
-      </c>
-      <c r="M15" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N15" s="39">
-        <v>50</v>
-      </c>
-      <c r="O15" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="P15" s="39">
-        <v>7.3000000000000001E-3</v>
-      </c>
-      <c r="Q15" s="42">
-        <f t="shared" si="1"/>
-        <v>0.36499999999999999</v>
-      </c>
-      <c r="R15" s="42"/>
-    </row>
-    <row r="16" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M15" s="42"/>
+    </row>
+    <row r="16" spans="1:13" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
       <c r="B16" s="53">
         <f t="shared" si="0"/>
@@ -2371,37 +2131,21 @@
         <v>103</v>
       </c>
       <c r="I16" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="J16" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="K16" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="J16" s="40" t="s">
         <v>121</v>
       </c>
+      <c r="K16" s="39">
+        <v>1</v>
+      </c>
       <c r="L16" s="39">
-        <v>1</v>
-      </c>
-      <c r="M16" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N16" s="39">
-        <v>100</v>
-      </c>
-      <c r="O16" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="P16" s="39">
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q16" s="42">
-        <f t="shared" si="1"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R16" s="42"/>
-    </row>
-    <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M16" s="42"/>
+    </row>
+    <row r="17" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
       <c r="B17" s="53">
         <f>ROW(B17) - ROW($B$9)</f>
@@ -2411,52 +2155,36 @@
         <v>135</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F17" s="37" t="s">
         <v>75</v>
       </c>
       <c r="G17" s="37" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="I17" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="J17" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="K17" s="38" t="s">
-        <v>156</v>
-      </c>
-      <c r="L17" s="70">
+        <v>161</v>
+      </c>
+      <c r="J17" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="K17" s="63">
         <v>1</v>
       </c>
-      <c r="M17" s="37">
-        <f t="shared" si="2"/>
+      <c r="L17" s="37">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N17" s="37">
-        <v>25</v>
-      </c>
-      <c r="O17" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P17" s="37">
-        <v>0.17119999999999999</v>
-      </c>
-      <c r="Q17" s="41">
-        <f t="shared" si="1"/>
-        <v>4.2799999999999994</v>
-      </c>
-      <c r="R17" s="69"/>
-    </row>
-    <row r="18" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M17" s="62"/>
+    </row>
+    <row r="18" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
       <c r="B18" s="53">
         <f t="shared" si="0"/>
@@ -2481,37 +2209,21 @@
         <v>108</v>
       </c>
       <c r="I18" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="J18" s="39" t="s">
-        <v>168</v>
-      </c>
-      <c r="K18" s="40" t="s">
-        <v>156</v>
+        <v>162</v>
+      </c>
+      <c r="J18" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="K18" s="39">
+        <v>1</v>
       </c>
       <c r="L18" s="39">
-        <v>1</v>
-      </c>
-      <c r="M18" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N18" s="39">
-        <v>25</v>
-      </c>
-      <c r="O18" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="P18" s="39">
-        <v>0.1066</v>
-      </c>
-      <c r="Q18" s="42">
-        <f t="shared" si="1"/>
-        <v>2.665</v>
-      </c>
-      <c r="R18" s="42"/>
-    </row>
-    <row r="19" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M18" s="42"/>
+    </row>
+    <row r="19" spans="1:13" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="53">
         <f>ROW(B19) - ROW($B$9)</f>
@@ -2527,7 +2239,7 @@
         <v>46</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G19" s="38" t="s">
         <v>70</v>
@@ -2536,37 +2248,21 @@
         <v>107</v>
       </c>
       <c r="I19" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="J19" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="K19" s="38" t="s">
-        <v>156</v>
+        <v>164</v>
+      </c>
+      <c r="J19" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="K19" s="37">
+        <v>4</v>
       </c>
       <c r="L19" s="37">
-        <v>4</v>
-      </c>
-      <c r="M19" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N19" s="37">
-        <v>100</v>
-      </c>
-      <c r="O19" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P19" s="37">
-        <v>2.9499999999999998E-2</v>
-      </c>
-      <c r="Q19" s="41">
-        <f t="shared" si="1"/>
-        <v>2.9499999999999997</v>
-      </c>
-      <c r="R19" s="41"/>
-    </row>
-    <row r="20" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M19" s="41"/>
+    </row>
+    <row r="20" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
       <c r="B20" s="53">
         <f t="shared" si="0"/>
@@ -2591,37 +2287,21 @@
         <v>109</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="J20" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="K20" s="40" t="s">
-        <v>156</v>
+        <v>151</v>
+      </c>
+      <c r="J20" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="K20" s="39">
+        <v>1</v>
       </c>
       <c r="L20" s="39">
-        <v>1</v>
-      </c>
-      <c r="M20" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N20" s="39">
-        <v>25</v>
-      </c>
-      <c r="O20" s="61" t="s">
-        <v>171</v>
-      </c>
-      <c r="P20" s="39">
-        <v>2.09</v>
-      </c>
-      <c r="Q20" s="42">
-        <f t="shared" si="1"/>
-        <v>52.25</v>
-      </c>
-      <c r="R20" s="42"/>
-    </row>
-    <row r="21" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M20" s="42"/>
+    </row>
+    <row r="21" spans="1:13" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
       <c r="B21" s="53">
         <f>ROW(B21) - ROW($B$9)</f>
@@ -2646,37 +2326,21 @@
         <v>110</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="J21" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="K21" s="38" t="s">
-        <v>156</v>
+        <v>165</v>
+      </c>
+      <c r="J21" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="K21" s="37">
+        <v>1</v>
       </c>
       <c r="L21" s="37">
-        <v>1</v>
-      </c>
-      <c r="M21" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N21" s="37">
-        <v>25</v>
-      </c>
-      <c r="O21" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P21" s="37">
-        <v>9.8500000000000004E-2</v>
-      </c>
-      <c r="Q21" s="41">
-        <f t="shared" si="1"/>
-        <v>2.4624999999999999</v>
-      </c>
-      <c r="R21" s="41"/>
-    </row>
-    <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M21" s="41"/>
+    </row>
+    <row r="22" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="1"/>
       <c r="B22" s="53">
         <f t="shared" si="0"/>
@@ -2695,43 +2359,27 @@
         <v>73</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="J22" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="K22" s="40" t="s">
-        <v>156</v>
+        <v>167</v>
+      </c>
+      <c r="J22" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="K22" s="39">
+        <v>1</v>
       </c>
       <c r="L22" s="39">
-        <v>1</v>
-      </c>
-      <c r="M22" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N22" s="39">
-        <v>30</v>
-      </c>
-      <c r="O22" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="P22" s="39">
-        <v>4.2200000000000001E-2</v>
-      </c>
-      <c r="Q22" s="42">
-        <f t="shared" si="1"/>
-        <v>1.266</v>
-      </c>
-      <c r="R22" s="42"/>
-    </row>
-    <row r="23" spans="1:18" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M22" s="42"/>
+    </row>
+    <row r="23" spans="1:13" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="1"/>
       <c r="B23" s="53">
         <f>ROW(B23) - ROW($B$9)</f>
@@ -2756,37 +2404,21 @@
         <v>111</v>
       </c>
       <c r="I23" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="J23" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="K23" s="38" t="s">
-        <v>156</v>
+        <v>151</v>
+      </c>
+      <c r="J23" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="K23" s="37">
+        <v>1</v>
       </c>
       <c r="L23" s="37">
-        <v>1</v>
-      </c>
-      <c r="M23" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N23" s="37">
-        <v>25</v>
-      </c>
-      <c r="O23" s="60" t="s">
-        <v>175</v>
-      </c>
-      <c r="P23" s="37">
-        <v>0.30840000000000001</v>
-      </c>
-      <c r="Q23" s="41">
-        <f t="shared" si="1"/>
-        <v>7.71</v>
-      </c>
-      <c r="R23" s="41"/>
-    </row>
-    <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M23" s="41"/>
+    </row>
+    <row r="24" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="1"/>
       <c r="B24" s="53">
         <f t="shared" si="0"/>
@@ -2811,37 +2443,21 @@
         <v>112</v>
       </c>
       <c r="I24" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="J24" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="K24" s="40" t="s">
-        <v>156</v>
+        <v>168</v>
+      </c>
+      <c r="J24" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="K24" s="39">
+        <v>2</v>
       </c>
       <c r="L24" s="39">
-        <v>2</v>
-      </c>
-      <c r="M24" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N24" s="39">
-        <v>60</v>
-      </c>
-      <c r="O24" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="P24" s="39">
-        <v>3.4799999999999998E-2</v>
-      </c>
-      <c r="Q24" s="42">
-        <f t="shared" si="1"/>
-        <v>2.0880000000000001</v>
-      </c>
-      <c r="R24" s="42"/>
-    </row>
-    <row r="25" spans="1:18" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M24" s="42"/>
+    </row>
+    <row r="25" spans="1:13" ht="48.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="53">
         <f>ROW(B25) - ROW($B$9)</f>
@@ -2866,37 +2482,21 @@
         <v>106</v>
       </c>
       <c r="I25" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="J25" s="37" t="s">
-        <v>177</v>
-      </c>
-      <c r="K25" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="J25" s="38" t="s">
         <v>126</v>
       </c>
+      <c r="K25" s="37">
+        <v>40</v>
+      </c>
       <c r="L25" s="37">
-        <v>40</v>
-      </c>
-      <c r="M25" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>800</v>
       </c>
-      <c r="N25" s="37">
-        <v>900</v>
-      </c>
-      <c r="O25" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P25" s="37">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="Q25" s="41">
-        <f t="shared" si="1"/>
-        <v>0.80999999999999994</v>
-      </c>
-      <c r="R25" s="41"/>
-    </row>
-    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M25" s="41"/>
+    </row>
+    <row r="26" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="1"/>
       <c r="B26" s="53">
         <f t="shared" si="0"/>
@@ -2921,37 +2521,21 @@
         <v>106</v>
       </c>
       <c r="I26" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="J26" s="39" t="s">
-        <v>178</v>
-      </c>
-      <c r="K26" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="J26" s="40" t="s">
         <v>127</v>
       </c>
+      <c r="K26" s="39">
+        <v>7</v>
+      </c>
       <c r="L26" s="39">
-        <v>7</v>
-      </c>
-      <c r="M26" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>140</v>
       </c>
-      <c r="N26" s="39">
-        <v>200</v>
-      </c>
-      <c r="O26" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="P26" s="39">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q26" s="42">
-        <f t="shared" si="1"/>
-        <v>0.24</v>
-      </c>
-      <c r="R26" s="42"/>
-    </row>
-    <row r="27" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M26" s="42"/>
+    </row>
+    <row r="27" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1"/>
       <c r="B27" s="53">
         <f>ROW(B27) - ROW($B$9)</f>
@@ -2964,49 +2548,33 @@
         <v>26</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="F27" s="37" t="s">
         <v>76</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="I27" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="J27" s="37" t="s">
-        <v>180</v>
-      </c>
-      <c r="K27" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="J27" s="38" t="s">
         <v>128</v>
       </c>
+      <c r="K27" s="37">
+        <v>1</v>
+      </c>
       <c r="L27" s="37">
-        <v>1</v>
-      </c>
-      <c r="M27" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N27" s="37">
-        <v>100</v>
-      </c>
-      <c r="O27" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P27" s="37">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="Q27" s="41">
-        <f t="shared" si="1"/>
-        <v>0.21</v>
-      </c>
-      <c r="R27" s="41"/>
-    </row>
-    <row r="28" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M27" s="41"/>
+    </row>
+    <row r="28" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="1"/>
       <c r="B28" s="53">
         <f t="shared" si="0"/>
@@ -3031,37 +2599,21 @@
         <v>106</v>
       </c>
       <c r="I28" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="J28" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="K28" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="J28" s="40" t="s">
         <v>129</v>
       </c>
+      <c r="K28" s="39">
+        <v>2</v>
+      </c>
       <c r="L28" s="39">
-        <v>2</v>
-      </c>
-      <c r="M28" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N28" s="39">
-        <v>100</v>
-      </c>
-      <c r="O28" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="P28" s="39">
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q28" s="42">
-        <f t="shared" si="1"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R28" s="42"/>
-    </row>
-    <row r="29" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M28" s="42"/>
+    </row>
+    <row r="29" spans="1:13" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="1"/>
       <c r="B29" s="53">
         <f>ROW(B29) - ROW($B$9)</f>
@@ -3070,8 +2622,8 @@
       <c r="C29" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="D29" s="74" t="s">
-        <v>204</v>
+      <c r="D29" s="67" t="s">
+        <v>193</v>
       </c>
       <c r="E29" s="38" t="s">
         <v>55</v>
@@ -3086,39 +2638,23 @@
         <v>106</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="J29" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="K29" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="J29" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="L29" s="75">
+      <c r="K29" s="68">
         <v>2</v>
       </c>
-      <c r="M29" s="37">
-        <f t="shared" si="2"/>
+      <c r="L29" s="37">
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N29" s="37">
-        <v>100</v>
-      </c>
-      <c r="O29" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P29" s="37">
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q29" s="41">
-        <f t="shared" si="1"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R29" s="69" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M29" s="62" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="1"/>
       <c r="B30" s="53">
         <f t="shared" si="0"/>
@@ -3131,162 +2667,114 @@
         <v>28</v>
       </c>
       <c r="E30" s="40" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="F30" s="39" t="s">
         <v>77</v>
       </c>
       <c r="G30" s="39" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="H30" s="39" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="I30" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="J30" s="39" t="s">
-        <v>184</v>
-      </c>
-      <c r="K30" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="J30" s="40" t="s">
         <v>131</v>
       </c>
+      <c r="K30" s="39">
+        <v>2</v>
+      </c>
       <c r="L30" s="39">
-        <v>2</v>
-      </c>
-      <c r="M30" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N30" s="39">
-        <v>50</v>
-      </c>
-      <c r="O30" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="P30" s="39">
-        <v>1.01E-2</v>
-      </c>
-      <c r="Q30" s="42">
-        <f t="shared" si="1"/>
-        <v>0.505</v>
-      </c>
-      <c r="R30" s="42"/>
-    </row>
-    <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M30" s="42"/>
+    </row>
+    <row r="31" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="1"/>
       <c r="B31" s="53">
         <v>22</v>
       </c>
-      <c r="C31" s="77" t="s">
+      <c r="C31" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="D31" s="72" t="s">
-        <v>200</v>
-      </c>
-      <c r="E31" s="78" t="s">
-        <v>206</v>
-      </c>
-      <c r="F31" s="72" t="s">
+      <c r="D31" s="65" t="s">
+        <v>189</v>
+      </c>
+      <c r="E31" s="71" t="s">
+        <v>195</v>
+      </c>
+      <c r="F31" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="G31" s="78" t="s">
-        <v>201</v>
-      </c>
-      <c r="H31" s="72" t="s">
+      <c r="G31" s="71" t="s">
+        <v>190</v>
+      </c>
+      <c r="H31" s="65" t="s">
         <v>106</v>
       </c>
-      <c r="I31" s="77" t="s">
-        <v>156</v>
-      </c>
-      <c r="J31" s="77" t="s">
-        <v>208</v>
-      </c>
-      <c r="K31" s="78" t="s">
-        <v>202</v>
-      </c>
-      <c r="L31" s="72">
+      <c r="I31" s="70" t="s">
+        <v>197</v>
+      </c>
+      <c r="J31" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="K31" s="65">
         <v>2</v>
       </c>
-      <c r="M31" s="72">
-        <f t="shared" ref="M31:M42" si="3">L31*20</f>
+      <c r="L31" s="65">
+        <f t="shared" ref="L31:L42" si="2">K31*20</f>
         <v>40</v>
       </c>
-      <c r="N31" s="77">
-        <v>100</v>
-      </c>
-      <c r="O31" s="79" t="s">
-        <v>158</v>
-      </c>
-      <c r="P31" s="77">
-        <v>1E-3</v>
-      </c>
-      <c r="Q31" s="80">
-        <f>P31*N31</f>
-        <v>0.1</v>
-      </c>
-      <c r="R31" s="81" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M31" s="72" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1"/>
       <c r="B32" s="53">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="62" t="s">
+      <c r="C32" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="D32" s="62" t="s">
+      <c r="D32" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="E32" s="63" t="s">
+      <c r="E32" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="F32" s="62" t="s">
+      <c r="F32" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="G32" s="63" t="s">
-        <v>156</v>
-      </c>
-      <c r="H32" s="62" t="s">
-        <v>156</v>
-      </c>
-      <c r="I32" s="62" t="s">
-        <v>156</v>
-      </c>
-      <c r="J32" s="62" t="s">
-        <v>156</v>
-      </c>
-      <c r="K32" s="63" t="s">
-        <v>156</v>
-      </c>
-      <c r="L32" s="62">
+      <c r="G32" s="60" t="s">
+        <v>151</v>
+      </c>
+      <c r="H32" s="59" t="s">
+        <v>151</v>
+      </c>
+      <c r="I32" s="59" t="s">
+        <v>151</v>
+      </c>
+      <c r="J32" s="60" t="s">
+        <v>151</v>
+      </c>
+      <c r="K32" s="59">
         <v>8</v>
       </c>
-      <c r="M32" s="62">
-        <f t="shared" si="3"/>
+      <c r="L32" s="59">
+        <f t="shared" si="2"/>
         <v>160</v>
       </c>
-      <c r="N32" s="62">
-        <v>160</v>
-      </c>
-      <c r="O32" s="62" t="s">
-        <v>156</v>
-      </c>
-      <c r="P32" s="62">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="64">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R32" s="64" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M32" s="61" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="1"/>
       <c r="B33" s="53">
         <f t="shared" si="0"/>
@@ -3299,49 +2787,33 @@
         <v>30</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F33" s="39" t="s">
         <v>145</v>
       </c>
       <c r="G33" s="39" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="H33" s="39" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="I33" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="J33" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="K33" s="40" t="s">
-        <v>156</v>
+        <v>179</v>
+      </c>
+      <c r="J33" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="K33" s="39">
+        <v>1</v>
       </c>
       <c r="L33" s="39">
-        <v>1</v>
-      </c>
-      <c r="M33" s="39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N33" s="39">
-        <v>30</v>
-      </c>
-      <c r="O33" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="P33" s="39">
-        <v>4.9599999999999998E-2</v>
-      </c>
-      <c r="Q33" s="42">
-        <f t="shared" si="1"/>
-        <v>1.488</v>
-      </c>
-      <c r="R33" s="71"/>
-    </row>
-    <row r="34" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M33" s="64"/>
+    </row>
+    <row r="34" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="1"/>
       <c r="B34" s="53">
         <f>ROW(B34) - ROW($B$9)</f>
@@ -3360,45 +2832,29 @@
         <v>146</v>
       </c>
       <c r="G34" s="38" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H34" s="37" t="s">
         <v>113</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>211</v>
-      </c>
-      <c r="J34" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="K34" s="38" t="s">
-        <v>156</v>
+        <v>198</v>
+      </c>
+      <c r="J34" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="K34" s="37">
+        <v>1</v>
       </c>
       <c r="L34" s="37">
-        <v>1</v>
-      </c>
-      <c r="M34" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N34" s="37">
-        <v>22</v>
-      </c>
-      <c r="O34" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P34" s="37">
-        <v>10.947699999999999</v>
-      </c>
-      <c r="Q34" s="41">
-        <f t="shared" si="1"/>
-        <v>240.84939999999997</v>
-      </c>
-      <c r="R34" s="69" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M34" s="62" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="1"/>
       <c r="B35" s="53">
         <f t="shared" si="0"/>
@@ -3417,43 +2873,27 @@
         <v>79</v>
       </c>
       <c r="G35" s="39" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="H35" s="39" t="s">
         <v>114</v>
       </c>
       <c r="I35" s="39" t="s">
-        <v>188</v>
-      </c>
-      <c r="J35" s="39" t="s">
-        <v>189</v>
-      </c>
-      <c r="K35" s="40" t="s">
-        <v>156</v>
+        <v>181</v>
+      </c>
+      <c r="J35" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="K35" s="39">
+        <v>1</v>
       </c>
       <c r="L35" s="39">
-        <v>1</v>
-      </c>
-      <c r="M35" s="39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N35" s="39">
-        <v>22</v>
-      </c>
-      <c r="O35" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="P35" s="39">
-        <v>3.0078999999999998</v>
-      </c>
-      <c r="Q35" s="42">
-        <f t="shared" si="1"/>
-        <v>66.1738</v>
-      </c>
-      <c r="R35" s="71"/>
-    </row>
-    <row r="36" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M35" s="64"/>
+    </row>
+    <row r="36" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="1"/>
       <c r="B36" s="53">
         <f>ROW(B36) - ROW($B$9)</f>
@@ -3466,49 +2906,33 @@
         <v>33</v>
       </c>
       <c r="E36" s="38" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="J36" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="K36" s="38" t="s">
-        <v>156</v>
+        <v>183</v>
+      </c>
+      <c r="J36" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="K36" s="37">
+        <v>1</v>
       </c>
       <c r="L36" s="37">
-        <v>1</v>
-      </c>
-      <c r="M36" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N36" s="37">
-        <v>22</v>
-      </c>
-      <c r="O36" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P36" s="37">
-        <v>4.2937000000000003</v>
-      </c>
-      <c r="Q36" s="41">
-        <f t="shared" si="1"/>
-        <v>94.461400000000012</v>
-      </c>
-      <c r="R36" s="69"/>
-    </row>
-    <row r="37" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M36" s="62"/>
+    </row>
+    <row r="37" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="1"/>
       <c r="B37" s="53">
         <f t="shared" si="0"/>
@@ -3533,37 +2957,21 @@
         <v>115</v>
       </c>
       <c r="I37" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="J37" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="K37" s="40" t="s">
-        <v>156</v>
+        <v>151</v>
+      </c>
+      <c r="J37" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="K37" s="39">
+        <v>1</v>
       </c>
       <c r="L37" s="39">
-        <v>1</v>
-      </c>
-      <c r="M37" s="39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N37" s="39">
-        <v>22</v>
-      </c>
-      <c r="O37" s="61" t="s">
-        <v>192</v>
-      </c>
-      <c r="P37" s="39">
-        <v>10.6416</v>
-      </c>
-      <c r="Q37" s="42">
-        <f t="shared" si="1"/>
-        <v>234.11520000000002</v>
-      </c>
-      <c r="R37" s="42"/>
-    </row>
-    <row r="38" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M37" s="42"/>
+    </row>
+    <row r="38" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="1"/>
       <c r="B38" s="53">
         <f>ROW(B38) - ROW($B$9)</f>
@@ -3588,37 +2996,21 @@
         <v>114</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="J38" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="K38" s="38" t="s">
-        <v>156</v>
+        <v>184</v>
+      </c>
+      <c r="J38" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="K38" s="37">
+        <v>1</v>
       </c>
       <c r="L38" s="37">
-        <v>1</v>
-      </c>
-      <c r="M38" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N38" s="37">
-        <v>22</v>
-      </c>
-      <c r="O38" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P38" s="37">
-        <v>0.3337</v>
-      </c>
-      <c r="Q38" s="41">
-        <f t="shared" si="1"/>
-        <v>7.3414000000000001</v>
-      </c>
-      <c r="R38" s="41"/>
-    </row>
-    <row r="39" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M38" s="41"/>
+    </row>
+    <row r="39" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="1"/>
       <c r="B39" s="53">
         <f t="shared" si="0"/>
@@ -3643,37 +3035,21 @@
         <v>116</v>
       </c>
       <c r="I39" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="J39" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="K39" s="40" t="s">
-        <v>156</v>
+        <v>151</v>
+      </c>
+      <c r="J39" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="K39" s="39">
+        <v>1</v>
       </c>
       <c r="L39" s="39">
-        <v>1</v>
-      </c>
-      <c r="M39" s="39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N39" s="39">
-        <v>22</v>
-      </c>
-      <c r="O39" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="P39" s="39">
-        <v>1.06</v>
-      </c>
-      <c r="Q39" s="42">
-        <f t="shared" si="1"/>
-        <v>23.32</v>
-      </c>
-      <c r="R39" s="42"/>
-    </row>
-    <row r="40" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M39" s="42"/>
+    </row>
+    <row r="40" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="1"/>
       <c r="B40" s="53">
         <f>ROW(B40) - ROW($B$9)</f>
@@ -3698,37 +3074,21 @@
         <v>108</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="J40" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="K40" s="38" t="s">
-        <v>156</v>
+        <v>185</v>
+      </c>
+      <c r="J40" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="K40" s="37">
+        <v>1</v>
       </c>
       <c r="L40" s="37">
-        <v>1</v>
-      </c>
-      <c r="M40" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N40" s="37">
-        <v>22</v>
-      </c>
-      <c r="O40" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P40" s="37">
-        <v>0.77</v>
-      </c>
-      <c r="Q40" s="41">
-        <f t="shared" si="1"/>
-        <v>16.940000000000001</v>
-      </c>
-      <c r="R40" s="41"/>
-    </row>
-    <row r="41" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M40" s="41"/>
+    </row>
+    <row r="41" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="1"/>
       <c r="B41" s="53">
         <f t="shared" si="0"/>
@@ -3753,37 +3113,21 @@
         <v>117</v>
       </c>
       <c r="I41" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="J41" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="K41" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="J41" s="40" t="s">
         <v>132</v>
       </c>
+      <c r="K41" s="39">
+        <v>1</v>
+      </c>
       <c r="L41" s="39">
-        <v>1</v>
-      </c>
-      <c r="M41" s="39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N41" s="39">
-        <v>22</v>
-      </c>
-      <c r="O41" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="P41" s="39">
-        <v>0.499</v>
-      </c>
-      <c r="Q41" s="42">
-        <f t="shared" si="1"/>
-        <v>10.978</v>
-      </c>
-      <c r="R41" s="42"/>
-    </row>
-    <row r="42" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M41" s="42"/>
+    </row>
+    <row r="42" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="1"/>
       <c r="B42" s="53">
         <f>ROW(B42) - ROW($B$9)</f>
@@ -3807,38 +3151,22 @@
       <c r="H42" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="I42" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="J42" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K42" s="38" t="s">
-        <v>195</v>
+      <c r="I42" s="58" t="s">
+        <v>151</v>
+      </c>
+      <c r="J42" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="K42" s="37">
+        <v>1</v>
       </c>
       <c r="L42" s="37">
-        <v>1</v>
-      </c>
-      <c r="M42" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N42" s="37">
-        <v>22</v>
-      </c>
-      <c r="O42" s="60" t="s">
-        <v>171</v>
-      </c>
-      <c r="P42" s="37">
-        <v>0.69</v>
-      </c>
-      <c r="Q42" s="41">
-        <f t="shared" si="1"/>
-        <v>15.18</v>
-      </c>
-      <c r="R42" s="41"/>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M42" s="41"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
       <c r="B43" s="32"/>
       <c r="C43" s="51"/>
@@ -3853,19 +3181,9 @@
       <c r="J43" s="36"/>
       <c r="K43" s="36"/>
       <c r="L43" s="36"/>
-      <c r="M43" s="36"/>
-      <c r="N43" s="36"/>
-      <c r="O43" s="65" t="s">
-        <v>196</v>
-      </c>
-      <c r="P43" s="66"/>
-      <c r="Q43" s="65">
-        <f>SUM(Q10:Q42)</f>
-        <v>794.87919999999997</v>
-      </c>
-      <c r="R43" s="44"/>
-    </row>
-    <row r="44" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M43" s="44"/>
+    </row>
+    <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="1"/>
       <c r="B44" s="24"/>
       <c r="C44" s="52"/>
@@ -3880,58 +3198,15 @@
       <c r="J44" s="9"/>
       <c r="K44" s="9"/>
       <c r="L44" s="9"/>
-      <c r="M44" s="9"/>
-      <c r="N44" s="9"/>
-      <c r="O44" s="67" t="s">
-        <v>197</v>
-      </c>
-      <c r="P44" s="68"/>
-      <c r="Q44" s="67">
-        <f>Q43/20</f>
-        <v>39.743960000000001</v>
-      </c>
-      <c r="R44" s="45"/>
+      <c r="M44" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="K1:R1"/>
-    <mergeCell ref="R3:R8"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="M3:M8"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1"/>
-    <hyperlink ref="O11" r:id="rId2"/>
-    <hyperlink ref="O12" r:id="rId3"/>
-    <hyperlink ref="O13" r:id="rId4"/>
-    <hyperlink ref="O14" r:id="rId5"/>
-    <hyperlink ref="O15" r:id="rId6"/>
-    <hyperlink ref="O17" r:id="rId7"/>
-    <hyperlink ref="O18" r:id="rId8"/>
-    <hyperlink ref="O19" r:id="rId9"/>
-    <hyperlink ref="O20" r:id="rId10"/>
-    <hyperlink ref="O21" r:id="rId11"/>
-    <hyperlink ref="O22" r:id="rId12"/>
-    <hyperlink ref="O23" r:id="rId13"/>
-    <hyperlink ref="O24" r:id="rId14"/>
-    <hyperlink ref="O25" r:id="rId15"/>
-    <hyperlink ref="O26" r:id="rId16"/>
-    <hyperlink ref="O27" r:id="rId17"/>
-    <hyperlink ref="O28" r:id="rId18"/>
-    <hyperlink ref="O29" r:id="rId19"/>
-    <hyperlink ref="O30" r:id="rId20"/>
-    <hyperlink ref="O33" r:id="rId21"/>
-    <hyperlink ref="O34" r:id="rId22"/>
-    <hyperlink ref="O35" r:id="rId23"/>
-    <hyperlink ref="O36" r:id="rId24"/>
-    <hyperlink ref="O37" r:id="rId25"/>
-    <hyperlink ref="O38" r:id="rId26"/>
-    <hyperlink ref="O39" r:id="rId27"/>
-    <hyperlink ref="O40" r:id="rId28"/>
-    <hyperlink ref="O41" r:id="rId29"/>
-    <hyperlink ref="O42" r:id="rId30"/>
-    <hyperlink ref="O31" r:id="rId31"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId32"/>
-  <drawing r:id="rId33"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Deliverables/SM_Bottom Board/_BOM/Supplier BOM_Bottom (20 Boards).xlsx
+++ b/Deliverables/SM_Bottom Board/_BOM/Supplier BOM_Bottom (20 Boards).xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="189">
   <si>
     <t>Component list</t>
   </si>
@@ -475,9 +475,6 @@
     <t>Item Type</t>
   </si>
   <si>
-    <t>LCSC Part Number</t>
-  </si>
-  <si>
     <t>Quantity (20 Boards)</t>
   </si>
   <si>
@@ -487,106 +484,37 @@
     <t>-</t>
   </si>
   <si>
-    <t>C69335</t>
-  </si>
-  <si>
-    <t>C1591</t>
-  </si>
-  <si>
     <t>TAJA105K016RNJ</t>
   </si>
   <si>
-    <t>C7174</t>
-  </si>
-  <si>
-    <t>C86017</t>
-  </si>
-  <si>
-    <t>C113797</t>
-  </si>
-  <si>
     <t>UMK063CG100DTHF</t>
   </si>
   <si>
-    <t>C2168858</t>
-  </si>
-  <si>
     <t>PESD2CAN,215</t>
   </si>
   <si>
-    <t>C75176</t>
-  </si>
-  <si>
-    <t>C82326</t>
-  </si>
-  <si>
     <t>Ferrite0603</t>
   </si>
   <si>
-    <t>C307770</t>
-  </si>
-  <si>
-    <t>C515365</t>
-  </si>
-  <si>
     <t>MHT136CGCT</t>
   </si>
   <si>
-    <t>C401111</t>
-  </si>
-  <si>
-    <t>C94515</t>
-  </si>
-  <si>
-    <t>C106228</t>
-  </si>
-  <si>
-    <t>C98220</t>
-  </si>
-  <si>
     <t>0201WMF8060TEE</t>
   </si>
   <si>
-    <t>C474262</t>
-  </si>
-  <si>
-    <t>C14676</t>
-  </si>
-  <si>
-    <t>C114669</t>
-  </si>
-  <si>
     <t>CR0603-FX-57R6ELF</t>
   </si>
   <si>
-    <t>C203694</t>
-  </si>
-  <si>
     <t>DO NOT MOUNT</t>
   </si>
   <si>
     <t>GT-TC025D-H0065-L1</t>
   </si>
   <si>
-    <t>C778132</t>
-  </si>
-  <si>
     <t>SN65HVDA1040AQDRQ1</t>
   </si>
   <si>
-    <t>C188675</t>
-  </si>
-  <si>
     <t>TLE5012BE1000</t>
-  </si>
-  <si>
-    <t>C123083</t>
-  </si>
-  <si>
-    <t>C100024</t>
-  </si>
-  <si>
-    <t>C233772</t>
   </si>
   <si>
     <t>32.768KHz</t>
@@ -632,12 +560,6 @@
   </si>
   <si>
     <t>Added due to Encoder IC</t>
-  </si>
-  <si>
-    <t>C105588</t>
-  </si>
-  <si>
-    <t>C12345, C28730</t>
   </si>
   <si>
     <t>Multiple options added for MCU</t>
@@ -892,7 +814,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1111,24 +1033,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1281,9 +1190,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1363,13 +1269,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>1905000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -1677,7 +1583,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="3.1796875" style="25" customWidth="1"/>
@@ -1687,15 +1593,14 @@
     <col min="6" max="6" width="26.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.453125" customWidth="1"/>
-    <col min="10" max="10" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.81640625" customWidth="1"/>
-    <col min="13" max="13" width="29.453125" customWidth="1"/>
-    <col min="15" max="15" width="18.26953125" customWidth="1"/>
+    <col min="9" max="9" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.81640625" customWidth="1"/>
+    <col min="12" max="12" width="29.453125" customWidth="1"/>
+    <col min="14" max="14" width="18.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1704,13 +1609,12 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-    </row>
-    <row r="2" spans="1:13" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+    </row>
+    <row r="2" spans="1:12" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="46"/>
@@ -1723,13 +1627,12 @@
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="11"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="43"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="L2" s="43"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="47"/>
@@ -1742,13 +1645,12 @@
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="12"/>
+      <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="74"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="L3" s="73"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="47"/>
@@ -1761,13 +1663,12 @@
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
-      <c r="I4" s="13"/>
+      <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="75"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="L4" s="74"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="47"/>
@@ -1780,13 +1681,12 @@
       </c>
       <c r="G5" s="14"/>
       <c r="H5" s="5"/>
-      <c r="I5" s="14"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="75"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="L5" s="74"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="48"/>
@@ -1795,13 +1695,12 @@
       <c r="F6" s="16"/>
       <c r="G6" s="14"/>
       <c r="H6" s="5"/>
-      <c r="I6" s="14"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="75"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="L6" s="74"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="49"/>
@@ -1810,13 +1709,12 @@
       <c r="F7" s="18"/>
       <c r="G7" s="17"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="17"/>
+      <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="75"/>
-    </row>
-    <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L7" s="74"/>
+    </row>
+    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="50"/>
@@ -1825,13 +1723,12 @@
       <c r="F8" s="28"/>
       <c r="G8" s="17"/>
       <c r="H8" s="7"/>
-      <c r="I8" s="17"/>
+      <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="75"/>
-    </row>
-    <row r="9" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L8" s="74"/>
+    </row>
+    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
@@ -1854,23 +1751,20 @@
       <c r="H9" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="K9" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="K9" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="L9" s="29" t="s">
+      <c r="L9" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="M9" s="31" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
       <c r="B10" s="53">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -1894,22 +1788,19 @@
       <c r="H10" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="I10" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="J10" s="38" t="s">
+      <c r="I10" s="38" t="s">
         <v>120</v>
       </c>
+      <c r="J10" s="37">
+        <v>1</v>
+      </c>
       <c r="K10" s="37">
-        <v>1</v>
-      </c>
-      <c r="L10" s="37">
-        <f>K10*20</f>
+        <f>J10*20</f>
         <v>20</v>
       </c>
-      <c r="M10" s="41"/>
-    </row>
-    <row r="11" spans="1:13" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L10" s="41"/>
+    </row>
+    <row r="11" spans="1:12" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
         <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
@@ -1919,7 +1810,7 @@
         <v>134</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="E11" s="40" t="s">
         <v>42</v>
@@ -1933,24 +1824,21 @@
       <c r="H11" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="I11" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="J11" s="40" t="s">
+      <c r="I11" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="K11" s="66">
+      <c r="J11" s="65">
         <v>18</v>
       </c>
-      <c r="L11" s="39">
-        <f>K11*20</f>
+      <c r="K11" s="39">
+        <f>J11*20</f>
         <v>360</v>
       </c>
-      <c r="M11" s="69" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L11" s="68" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
       <c r="B12" s="53">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -1963,33 +1851,30 @@
         <v>12</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="F12" s="37" t="s">
         <v>145</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H12" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="I12" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="J12" s="38" t="s">
+      <c r="I12" s="38" t="s">
         <v>122</v>
       </c>
+      <c r="J12" s="37">
+        <v>1</v>
+      </c>
       <c r="K12" s="37">
-        <v>1</v>
-      </c>
-      <c r="L12" s="37">
-        <f t="shared" ref="L12:L30" si="1">K12*20</f>
+        <f t="shared" ref="K12:K30" si="1">J12*20</f>
         <v>20</v>
       </c>
-      <c r="M12" s="62"/>
-    </row>
-    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L12" s="61"/>
+    </row>
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="53">
         <f t="shared" si="0"/>
@@ -2013,22 +1898,19 @@
       <c r="H13" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="I13" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="J13" s="40" t="s">
+      <c r="I13" s="40" t="s">
         <v>123</v>
       </c>
+      <c r="J13" s="39">
+        <v>2</v>
+      </c>
       <c r="K13" s="39">
-        <v>2</v>
-      </c>
-      <c r="L13" s="39">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="M13" s="42"/>
-    </row>
-    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L13" s="42"/>
+    </row>
+    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
       <c r="B14" s="53">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -2052,22 +1934,19 @@
       <c r="H14" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="I14" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="J14" s="38" t="s">
+      <c r="I14" s="38" t="s">
         <v>124</v>
       </c>
+      <c r="J14" s="37">
+        <v>2</v>
+      </c>
       <c r="K14" s="37">
-        <v>2</v>
-      </c>
-      <c r="L14" s="37">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="M14" s="41"/>
-    </row>
-    <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L14" s="41"/>
+    </row>
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
       <c r="B15" s="53">
         <f t="shared" si="0"/>
@@ -2080,33 +1959,30 @@
         <v>15</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="F15" s="39" t="s">
         <v>68</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="H15" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="I15" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="J15" s="40" t="s">
+      <c r="I15" s="40" t="s">
         <v>125</v>
       </c>
+      <c r="J15" s="39">
+        <v>2</v>
+      </c>
       <c r="K15" s="39">
-        <v>2</v>
-      </c>
-      <c r="L15" s="39">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="M15" s="42"/>
-    </row>
-    <row r="16" spans="1:13" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L15" s="42"/>
+    </row>
+    <row r="16" spans="1:12" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
       <c r="B16" s="53">
         <f t="shared" si="0"/>
@@ -2130,22 +2006,19 @@
       <c r="H16" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="I16" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="J16" s="40" t="s">
+      <c r="I16" s="40" t="s">
         <v>121</v>
       </c>
+      <c r="J16" s="39">
+        <v>1</v>
+      </c>
       <c r="K16" s="39">
-        <v>1</v>
-      </c>
-      <c r="L16" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="M16" s="42"/>
-    </row>
-    <row r="17" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L16" s="42"/>
+    </row>
+    <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
       <c r="B17" s="53">
         <f>ROW(B17) - ROW($B$9)</f>
@@ -2155,36 +2028,33 @@
         <v>135</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="F17" s="37" t="s">
         <v>75</v>
       </c>
       <c r="G17" s="37" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="I17" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="J17" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="K17" s="63">
+        <v>176</v>
+      </c>
+      <c r="I17" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="J17" s="62">
         <v>1</v>
       </c>
-      <c r="L17" s="37">
+      <c r="K17" s="37">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="M17" s="62"/>
-    </row>
-    <row r="18" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L17" s="61"/>
+    </row>
+    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
       <c r="B18" s="53">
         <f t="shared" si="0"/>
@@ -2208,22 +2078,19 @@
       <c r="H18" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="I18" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="J18" s="40" t="s">
-        <v>151</v>
+      <c r="I18" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="J18" s="39">
+        <v>1</v>
       </c>
       <c r="K18" s="39">
-        <v>1</v>
-      </c>
-      <c r="L18" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="M18" s="42"/>
-    </row>
-    <row r="19" spans="1:13" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L18" s="42"/>
+    </row>
+    <row r="19" spans="1:12" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="53">
         <f>ROW(B19) - ROW($B$9)</f>
@@ -2239,7 +2106,7 @@
         <v>46</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="G19" s="38" t="s">
         <v>70</v>
@@ -2247,22 +2114,19 @@
       <c r="H19" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="I19" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="J19" s="38" t="s">
-        <v>151</v>
+      <c r="I19" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="J19" s="37">
+        <v>4</v>
       </c>
       <c r="K19" s="37">
-        <v>4</v>
-      </c>
-      <c r="L19" s="37">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="M19" s="41"/>
-    </row>
-    <row r="20" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L19" s="41"/>
+    </row>
+    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
       <c r="B20" s="53">
         <f t="shared" si="0"/>
@@ -2286,22 +2150,19 @@
       <c r="H20" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="I20" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="J20" s="40" t="s">
-        <v>151</v>
+      <c r="I20" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="J20" s="39">
+        <v>1</v>
       </c>
       <c r="K20" s="39">
-        <v>1</v>
-      </c>
-      <c r="L20" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="M20" s="42"/>
-    </row>
-    <row r="21" spans="1:13" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L20" s="42"/>
+    </row>
+    <row r="21" spans="1:12" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
       <c r="B21" s="53">
         <f>ROW(B21) - ROW($B$9)</f>
@@ -2325,22 +2186,19 @@
       <c r="H21" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="I21" s="37" t="s">
-        <v>165</v>
-      </c>
-      <c r="J21" s="38" t="s">
-        <v>151</v>
+      <c r="I21" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="J21" s="37">
+        <v>1</v>
       </c>
       <c r="K21" s="37">
-        <v>1</v>
-      </c>
-      <c r="L21" s="37">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="M21" s="41"/>
-    </row>
-    <row r="22" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L21" s="41"/>
+    </row>
+    <row r="22" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="1"/>
       <c r="B22" s="53">
         <f t="shared" si="0"/>
@@ -2359,27 +2217,24 @@
         <v>73</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="I22" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="J22" s="40" t="s">
-        <v>151</v>
+        <v>178</v>
+      </c>
+      <c r="I22" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="J22" s="39">
+        <v>1</v>
       </c>
       <c r="K22" s="39">
-        <v>1</v>
-      </c>
-      <c r="L22" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="M22" s="42"/>
-    </row>
-    <row r="23" spans="1:13" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L22" s="42"/>
+    </row>
+    <row r="23" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="1"/>
       <c r="B23" s="53">
         <f>ROW(B23) - ROW($B$9)</f>
@@ -2403,22 +2258,19 @@
       <c r="H23" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="I23" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="J23" s="38" t="s">
-        <v>151</v>
+      <c r="I23" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="J23" s="37">
+        <v>1</v>
       </c>
       <c r="K23" s="37">
-        <v>1</v>
-      </c>
-      <c r="L23" s="37">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="M23" s="41"/>
-    </row>
-    <row r="24" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L23" s="41"/>
+    </row>
+    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="1"/>
       <c r="B24" s="53">
         <f t="shared" si="0"/>
@@ -2442,22 +2294,19 @@
       <c r="H24" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="I24" s="39" t="s">
-        <v>168</v>
-      </c>
-      <c r="J24" s="40" t="s">
-        <v>151</v>
+      <c r="I24" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="J24" s="39">
+        <v>2</v>
       </c>
       <c r="K24" s="39">
-        <v>2</v>
-      </c>
-      <c r="L24" s="39">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="M24" s="42"/>
-    </row>
-    <row r="25" spans="1:13" ht="48.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L24" s="42"/>
+    </row>
+    <row r="25" spans="1:12" ht="48.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="53">
         <f>ROW(B25) - ROW($B$9)</f>
@@ -2481,22 +2330,19 @@
       <c r="H25" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="I25" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="J25" s="38" t="s">
+      <c r="I25" s="38" t="s">
         <v>126</v>
       </c>
+      <c r="J25" s="37">
+        <v>40</v>
+      </c>
       <c r="K25" s="37">
-        <v>40</v>
-      </c>
-      <c r="L25" s="37">
         <f t="shared" si="1"/>
         <v>800</v>
       </c>
-      <c r="M25" s="41"/>
-    </row>
-    <row r="26" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L25" s="41"/>
+    </row>
+    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="1"/>
       <c r="B26" s="53">
         <f t="shared" si="0"/>
@@ -2520,22 +2366,19 @@
       <c r="H26" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="I26" s="39" t="s">
-        <v>170</v>
-      </c>
-      <c r="J26" s="40" t="s">
+      <c r="I26" s="40" t="s">
         <v>127</v>
       </c>
+      <c r="J26" s="39">
+        <v>7</v>
+      </c>
       <c r="K26" s="39">
-        <v>7</v>
-      </c>
-      <c r="L26" s="39">
         <f t="shared" si="1"/>
         <v>140</v>
       </c>
-      <c r="M26" s="42"/>
-    </row>
-    <row r="27" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L26" s="42"/>
+    </row>
+    <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1"/>
       <c r="B27" s="53">
         <f>ROW(B27) - ROW($B$9)</f>
@@ -2548,33 +2391,30 @@
         <v>26</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="F27" s="37" t="s">
         <v>76</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>205</v>
-      </c>
-      <c r="I27" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="J27" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="I27" s="38" t="s">
         <v>128</v>
       </c>
+      <c r="J27" s="37">
+        <v>1</v>
+      </c>
       <c r="K27" s="37">
-        <v>1</v>
-      </c>
-      <c r="L27" s="37">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="M27" s="41"/>
-    </row>
-    <row r="28" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L27" s="41"/>
+    </row>
+    <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="1"/>
       <c r="B28" s="53">
         <f t="shared" si="0"/>
@@ -2598,22 +2438,19 @@
       <c r="H28" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="I28" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="J28" s="40" t="s">
+      <c r="I28" s="40" t="s">
         <v>129</v>
       </c>
+      <c r="J28" s="39">
+        <v>2</v>
+      </c>
       <c r="K28" s="39">
-        <v>2</v>
-      </c>
-      <c r="L28" s="39">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="M28" s="42"/>
-    </row>
-    <row r="29" spans="1:13" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L28" s="42"/>
+    </row>
+    <row r="29" spans="1:12" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="1"/>
       <c r="B29" s="53">
         <f>ROW(B29) - ROW($B$9)</f>
@@ -2622,8 +2459,8 @@
       <c r="C29" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="D29" s="67" t="s">
-        <v>193</v>
+      <c r="D29" s="66" t="s">
+        <v>169</v>
       </c>
       <c r="E29" s="38" t="s">
         <v>55</v>
@@ -2637,24 +2474,21 @@
       <c r="H29" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="I29" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="J29" s="38" t="s">
+      <c r="I29" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="K29" s="68">
+      <c r="J29" s="67">
         <v>2</v>
       </c>
-      <c r="L29" s="37">
+      <c r="K29" s="37">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="M29" s="62" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L29" s="61" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="1"/>
       <c r="B30" s="53">
         <f t="shared" si="0"/>
@@ -2667,114 +2501,105 @@
         <v>28</v>
       </c>
       <c r="E30" s="40" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="F30" s="39" t="s">
         <v>77</v>
       </c>
       <c r="G30" s="39" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="H30" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="I30" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="J30" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="I30" s="40" t="s">
         <v>131</v>
       </c>
+      <c r="J30" s="39">
+        <v>2</v>
+      </c>
       <c r="K30" s="39">
-        <v>2</v>
-      </c>
-      <c r="L30" s="39">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="M30" s="42"/>
-    </row>
-    <row r="31" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L30" s="42"/>
+    </row>
+    <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="1"/>
       <c r="B31" s="53">
         <v>22</v>
       </c>
-      <c r="C31" s="70" t="s">
+      <c r="C31" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="D31" s="65" t="s">
-        <v>189</v>
-      </c>
-      <c r="E31" s="71" t="s">
-        <v>195</v>
-      </c>
-      <c r="F31" s="65" t="s">
+      <c r="D31" s="64" t="s">
+        <v>165</v>
+      </c>
+      <c r="E31" s="70" t="s">
+        <v>171</v>
+      </c>
+      <c r="F31" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="G31" s="71" t="s">
-        <v>190</v>
-      </c>
-      <c r="H31" s="65" t="s">
+      <c r="G31" s="70" t="s">
+        <v>166</v>
+      </c>
+      <c r="H31" s="64" t="s">
         <v>106</v>
       </c>
       <c r="I31" s="70" t="s">
-        <v>197</v>
-      </c>
-      <c r="J31" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="K31" s="65">
+        <v>167</v>
+      </c>
+      <c r="J31" s="64">
         <v>2</v>
       </c>
-      <c r="L31" s="65">
-        <f t="shared" ref="L31:L42" si="2">K31*20</f>
+      <c r="K31" s="64">
+        <f t="shared" ref="K31:K42" si="2">J31*20</f>
         <v>40</v>
       </c>
-      <c r="M31" s="72" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L31" s="71" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1"/>
       <c r="B32" s="53">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="59" t="s">
+      <c r="C32" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="D32" s="59" t="s">
+      <c r="D32" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="E32" s="60" t="s">
+      <c r="E32" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="F32" s="59" t="s">
+      <c r="F32" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="G32" s="60" t="s">
-        <v>151</v>
-      </c>
-      <c r="H32" s="59" t="s">
-        <v>151</v>
+      <c r="G32" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="H32" s="58" t="s">
+        <v>150</v>
       </c>
       <c r="I32" s="59" t="s">
-        <v>151</v>
-      </c>
-      <c r="J32" s="60" t="s">
-        <v>151</v>
-      </c>
-      <c r="K32" s="59">
+        <v>150</v>
+      </c>
+      <c r="J32" s="58">
         <v>8</v>
       </c>
-      <c r="L32" s="59">
+      <c r="K32" s="58">
         <f t="shared" si="2"/>
         <v>160</v>
       </c>
-      <c r="M32" s="61" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L32" s="60" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="1"/>
       <c r="B33" s="53">
         <f t="shared" si="0"/>
@@ -2787,33 +2612,30 @@
         <v>30</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="F33" s="39" t="s">
         <v>145</v>
       </c>
       <c r="G33" s="39" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="H33" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="I33" s="39" t="s">
-        <v>179</v>
-      </c>
-      <c r="J33" s="40" t="s">
-        <v>151</v>
+        <v>183</v>
+      </c>
+      <c r="I33" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="J33" s="39">
+        <v>1</v>
       </c>
       <c r="K33" s="39">
-        <v>1</v>
-      </c>
-      <c r="L33" s="39">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="M33" s="64"/>
-    </row>
-    <row r="34" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L33" s="63"/>
+    </row>
+    <row r="34" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="1"/>
       <c r="B34" s="53">
         <f>ROW(B34) - ROW($B$9)</f>
@@ -2832,29 +2654,26 @@
         <v>146</v>
       </c>
       <c r="G34" s="38" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="H34" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="I34" s="37" t="s">
-        <v>198</v>
-      </c>
-      <c r="J34" s="38" t="s">
-        <v>151</v>
+      <c r="I34" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="J34" s="37">
+        <v>1</v>
       </c>
       <c r="K34" s="37">
-        <v>1</v>
-      </c>
-      <c r="L34" s="37">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="M34" s="62" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L34" s="61" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="1"/>
       <c r="B35" s="53">
         <f t="shared" si="0"/>
@@ -2873,27 +2692,24 @@
         <v>79</v>
       </c>
       <c r="G35" s="39" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="H35" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="I35" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="J35" s="40" t="s">
-        <v>151</v>
+      <c r="I35" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="J35" s="39">
+        <v>1</v>
       </c>
       <c r="K35" s="39">
-        <v>1</v>
-      </c>
-      <c r="L35" s="39">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="M35" s="64"/>
-    </row>
-    <row r="36" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L35" s="63"/>
+    </row>
+    <row r="36" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="1"/>
       <c r="B36" s="53">
         <f>ROW(B36) - ROW($B$9)</f>
@@ -2906,33 +2722,30 @@
         <v>33</v>
       </c>
       <c r="E36" s="38" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="I36" s="37" t="s">
-        <v>183</v>
-      </c>
-      <c r="J36" s="38" t="s">
-        <v>151</v>
+        <v>186</v>
+      </c>
+      <c r="I36" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="J36" s="37">
+        <v>1</v>
       </c>
       <c r="K36" s="37">
-        <v>1</v>
-      </c>
-      <c r="L36" s="37">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="M36" s="62"/>
-    </row>
-    <row r="37" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L36" s="61"/>
+    </row>
+    <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="1"/>
       <c r="B37" s="53">
         <f t="shared" si="0"/>
@@ -2956,22 +2769,19 @@
       <c r="H37" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="I37" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="J37" s="40" t="s">
-        <v>151</v>
+      <c r="I37" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="J37" s="39">
+        <v>1</v>
       </c>
       <c r="K37" s="39">
-        <v>1</v>
-      </c>
-      <c r="L37" s="39">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="M37" s="42"/>
-    </row>
-    <row r="38" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L37" s="42"/>
+    </row>
+    <row r="38" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="1"/>
       <c r="B38" s="53">
         <f>ROW(B38) - ROW($B$9)</f>
@@ -2995,22 +2805,19 @@
       <c r="H38" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="I38" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="J38" s="38" t="s">
-        <v>151</v>
+      <c r="I38" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="J38" s="37">
+        <v>1</v>
       </c>
       <c r="K38" s="37">
-        <v>1</v>
-      </c>
-      <c r="L38" s="37">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="M38" s="41"/>
-    </row>
-    <row r="39" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L38" s="41"/>
+    </row>
+    <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="1"/>
       <c r="B39" s="53">
         <f t="shared" si="0"/>
@@ -3034,22 +2841,19 @@
       <c r="H39" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="I39" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="J39" s="40" t="s">
-        <v>151</v>
+      <c r="I39" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="J39" s="39">
+        <v>1</v>
       </c>
       <c r="K39" s="39">
-        <v>1</v>
-      </c>
-      <c r="L39" s="39">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="M39" s="42"/>
-    </row>
-    <row r="40" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L39" s="42"/>
+    </row>
+    <row r="40" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="1"/>
       <c r="B40" s="53">
         <f>ROW(B40) - ROW($B$9)</f>
@@ -3073,22 +2877,19 @@
       <c r="H40" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="I40" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="J40" s="38" t="s">
-        <v>151</v>
+      <c r="I40" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="J40" s="37">
+        <v>1</v>
       </c>
       <c r="K40" s="37">
-        <v>1</v>
-      </c>
-      <c r="L40" s="37">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="M40" s="41"/>
-    </row>
-    <row r="41" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L40" s="41"/>
+    </row>
+    <row r="41" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="1"/>
       <c r="B41" s="53">
         <f t="shared" si="0"/>
@@ -3112,22 +2913,19 @@
       <c r="H41" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="I41" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="J41" s="40" t="s">
+      <c r="I41" s="40" t="s">
         <v>132</v>
       </c>
+      <c r="J41" s="39">
+        <v>1</v>
+      </c>
       <c r="K41" s="39">
-        <v>1</v>
-      </c>
-      <c r="L41" s="39">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="M41" s="42"/>
-    </row>
-    <row r="42" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L41" s="42"/>
+    </row>
+    <row r="42" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="1"/>
       <c r="B42" s="53">
         <f>ROW(B42) - ROW($B$9)</f>
@@ -3151,22 +2949,19 @@
       <c r="H42" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="I42" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="J42" s="38" t="s">
-        <v>186</v>
+      <c r="I42" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="J42" s="37">
+        <v>1</v>
       </c>
       <c r="K42" s="37">
-        <v>1</v>
-      </c>
-      <c r="L42" s="37">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="M42" s="41"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="L42" s="41"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
       <c r="B43" s="32"/>
       <c r="C43" s="51"/>
@@ -3180,10 +2975,9 @@
       <c r="I43" s="36"/>
       <c r="J43" s="36"/>
       <c r="K43" s="36"/>
-      <c r="L43" s="36"/>
-      <c r="M43" s="44"/>
-    </row>
-    <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L43" s="44"/>
+    </row>
+    <row r="44" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="1"/>
       <c r="B44" s="24"/>
       <c r="C44" s="52"/>
@@ -3197,13 +2991,12 @@
       <c r="I44" s="9"/>
       <c r="J44" s="9"/>
       <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-      <c r="M44" s="45"/>
+      <c r="L44" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="M3:M8"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="L3:L8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Deliverables/SM_Bottom Board/_BOM/Supplier BOM_Bottom (20 Boards).xlsx
+++ b/Deliverables/SM_Bottom Board/_BOM/Supplier BOM_Bottom (20 Boards).xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Bottom Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Bottom Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="188">
   <si>
     <t>Component list</t>
   </si>
@@ -208,9 +208,6 @@
     <t>IC TRANSCEIVER 1/1 8SOIC</t>
   </si>
   <si>
-    <t>WIDE-FULL SCALE RANGE 6-AXIS MEM</t>
-  </si>
-  <si>
     <t>IC BUF NON-INVERT 5.5V SOT23-5</t>
   </si>
   <si>
@@ -271,9 +268,6 @@
     <t>SOIC-8</t>
   </si>
   <si>
-    <t>24-QFN (3x3)</t>
-  </si>
-  <si>
     <t>SOT-23-5</t>
   </si>
   <si>
@@ -325,9 +319,6 @@
     <t>RC0603FR-07470RL</t>
   </si>
   <si>
-    <t>ICM-20649</t>
-  </si>
-  <si>
     <t>SN74LV1T34DBVR</t>
   </si>
   <si>
@@ -374,9 +365,6 @@
   </si>
   <si>
     <t>Texas Instruments</t>
-  </si>
-  <si>
-    <t>TDK InvenSense</t>
   </si>
   <si>
     <t>Microchip</t>
@@ -609,11 +597,20 @@
   <si>
     <t>PG-DSO-8 Position Sensor ROHS</t>
   </si>
+  <si>
+    <t>LGA-14 Attitude Sensor/Gyroscope</t>
+  </si>
+  <si>
+    <t>LGA-14</t>
+  </si>
+  <si>
+    <t>LSM6DSLTR</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
@@ -629,6 +626,7 @@
       <sz val="10"/>
       <color indexed="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1285,7 +1283,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1584,23 +1582,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:L44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.1796875" style="25" customWidth="1"/>
-    <col min="3" max="3" width="18.7265625" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.81640625" customWidth="1"/>
-    <col min="12" max="12" width="29.453125" customWidth="1"/>
-    <col min="14" max="14" width="18.26953125" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.85546875" customWidth="1"/>
+    <col min="12" max="12" width="29.42578125" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1614,7 +1612,7 @@
       <c r="K1" s="72"/>
       <c r="L1" s="72"/>
     </row>
-    <row r="2" spans="1:12" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="46"/>
@@ -1632,7 +1630,7 @@
       <c r="K2" s="3"/>
       <c r="L2" s="43"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="47"/>
@@ -1650,7 +1648,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="73"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="47"/>
@@ -1668,7 +1666,7 @@
       <c r="K4" s="6"/>
       <c r="L4" s="74"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="47"/>
@@ -1686,7 +1684,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="74"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="48"/>
@@ -1700,7 +1698,7 @@
       <c r="K6" s="5"/>
       <c r="L6" s="74"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="49"/>
@@ -1714,7 +1712,7 @@
       <c r="K7" s="7"/>
       <c r="L7" s="74"/>
     </row>
-    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="50"/>
@@ -1728,13 +1726,13 @@
       <c r="K8" s="7"/>
       <c r="L8" s="74"/>
     </row>
-    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>10</v>
@@ -1743,35 +1741,35 @@
         <v>40</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="K9" s="29" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L9" s="31" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="53">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>11</v>
@@ -1780,16 +1778,16 @@
         <v>41</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="J10" s="37">
         <v>1</v>
@@ -1800,32 +1798,32 @@
       </c>
       <c r="L10" s="41"/>
     </row>
-    <row r="11" spans="1:12" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
         <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E11" s="40" t="s">
         <v>42</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I11" s="40" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J11" s="65">
         <v>18</v>
@@ -1835,35 +1833,35 @@
         <v>360</v>
       </c>
       <c r="L11" s="68" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="53">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D12" s="37" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J12" s="37">
         <v>1</v>
@@ -1874,14 +1872,14 @@
       </c>
       <c r="L12" s="61"/>
     </row>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="53">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D13" s="39" t="s">
         <v>13</v>
@@ -1890,16 +1888,16 @@
         <v>43</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I13" s="40" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J13" s="39">
         <v>2</v>
@@ -1910,14 +1908,14 @@
       </c>
       <c r="L13" s="42"/>
     </row>
-    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="53">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D14" s="37" t="s">
         <v>14</v>
@@ -1926,16 +1924,16 @@
         <v>44</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="J14" s="37">
         <v>2</v>
@@ -1946,32 +1944,32 @@
       </c>
       <c r="L14" s="41"/>
     </row>
-    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="53">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D15" s="39" t="s">
         <v>15</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I15" s="40" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="J15" s="39">
         <v>2</v>
@@ -1982,14 +1980,14 @@
       </c>
       <c r="L15" s="42"/>
     </row>
-    <row r="16" spans="1:12" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="53">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D16" s="39" t="s">
         <v>16</v>
@@ -1998,16 +1996,16 @@
         <v>42</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G16" s="40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I16" s="40" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J16" s="39">
         <v>1</v>
@@ -2018,32 +2016,32 @@
       </c>
       <c r="L16" s="42"/>
     </row>
-    <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="53">
         <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G17" s="37" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="I17" s="38" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J17" s="62">
         <v>1</v>
@@ -2054,14 +2052,14 @@
       </c>
       <c r="L17" s="61"/>
     </row>
-    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="53">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D18" s="39" t="s">
         <v>17</v>
@@ -2070,16 +2068,16 @@
         <v>45</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G18" s="40" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H18" s="39" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I18" s="40" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J18" s="39">
         <v>1</v>
@@ -2090,14 +2088,14 @@
       </c>
       <c r="L18" s="42"/>
     </row>
-    <row r="19" spans="1:12" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="53">
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D19" s="37" t="s">
         <v>18</v>
@@ -2106,16 +2104,16 @@
         <v>46</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I19" s="38" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J19" s="37">
         <v>4</v>
@@ -2126,14 +2124,14 @@
       </c>
       <c r="L19" s="41"/>
     </row>
-    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="53">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D20" s="39" t="s">
         <v>19</v>
@@ -2142,16 +2140,16 @@
         <v>47</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G20" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H20" s="39" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I20" s="40" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J20" s="39">
         <v>1</v>
@@ -2162,14 +2160,14 @@
       </c>
       <c r="L20" s="42"/>
     </row>
-    <row r="21" spans="1:12" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="53">
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D21" s="37" t="s">
         <v>20</v>
@@ -2178,16 +2176,16 @@
         <v>48</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I21" s="38" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J21" s="37">
         <v>1</v>
@@ -2198,14 +2196,14 @@
       </c>
       <c r="L21" s="41"/>
     </row>
-    <row r="22" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="53">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D22" s="39" t="s">
         <v>21</v>
@@ -2214,16 +2212,16 @@
         <v>49</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I22" s="40" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J22" s="39">
         <v>1</v>
@@ -2234,14 +2232,14 @@
       </c>
       <c r="L22" s="42"/>
     </row>
-    <row r="23" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="53">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D23" s="37" t="s">
         <v>22</v>
@@ -2250,16 +2248,16 @@
         <v>50</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I23" s="38" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J23" s="37">
         <v>1</v>
@@ -2270,14 +2268,14 @@
       </c>
       <c r="L23" s="41"/>
     </row>
-    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="53">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D24" s="39" t="s">
         <v>23</v>
@@ -2286,16 +2284,16 @@
         <v>51</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G24" s="40" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H24" s="39" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I24" s="40" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J24" s="39">
         <v>2</v>
@@ -2306,14 +2304,14 @@
       </c>
       <c r="L24" s="42"/>
     </row>
-    <row r="25" spans="1:12" ht="48.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:12" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="53">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D25" s="37" t="s">
         <v>24</v>
@@ -2322,16 +2320,16 @@
         <v>52</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G25" s="38" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I25" s="38" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J25" s="37">
         <v>40</v>
@@ -2342,14 +2340,14 @@
       </c>
       <c r="L25" s="41"/>
     </row>
-    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="53">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D26" s="39" t="s">
         <v>25</v>
@@ -2358,16 +2356,16 @@
         <v>53</v>
       </c>
       <c r="F26" s="39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G26" s="40" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H26" s="39" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I26" s="40" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J26" s="39">
         <v>7</v>
@@ -2378,32 +2376,32 @@
       </c>
       <c r="L26" s="42"/>
     </row>
-    <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="53">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D27" s="37" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I27" s="38" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J27" s="37">
         <v>1</v>
@@ -2414,14 +2412,14 @@
       </c>
       <c r="L27" s="41"/>
     </row>
-    <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="53">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D28" s="39" t="s">
         <v>27</v>
@@ -2430,16 +2428,16 @@
         <v>54</v>
       </c>
       <c r="F28" s="39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G28" s="40" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H28" s="39" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I28" s="40" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J28" s="39">
         <v>2</v>
@@ -2450,32 +2448,32 @@
       </c>
       <c r="L28" s="42"/>
     </row>
-    <row r="29" spans="1:12" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="53">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D29" s="66" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E29" s="38" t="s">
         <v>55</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G29" s="38" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I29" s="38" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="J29" s="67">
         <v>2</v>
@@ -2485,35 +2483,35 @@
         <v>40</v>
       </c>
       <c r="L29" s="61" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="53">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D30" s="39" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="40" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F30" s="39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G30" s="39" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H30" s="39" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I30" s="40" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="J30" s="39">
         <v>2</v>
@@ -2524,31 +2522,31 @@
       </c>
       <c r="L30" s="42"/>
     </row>
-    <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="53">
         <v>22</v>
       </c>
       <c r="C31" s="69" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D31" s="64" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E31" s="70" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F31" s="64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G31" s="70" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H31" s="64" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I31" s="70" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J31" s="64">
         <v>2</v>
@@ -2558,17 +2556,17 @@
         <v>40</v>
       </c>
       <c r="L31" s="71" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="53">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
       <c r="C32" s="58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D32" s="58" t="s">
         <v>29</v>
@@ -2577,16 +2575,16 @@
         <v>56</v>
       </c>
       <c r="F32" s="58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G32" s="59" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H32" s="58" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I32" s="59" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J32" s="58">
         <v>8</v>
@@ -2596,35 +2594,35 @@
         <v>160</v>
       </c>
       <c r="L32" s="60" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="53">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C33" s="39" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D33" s="39" t="s">
         <v>30</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F33" s="39" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G33" s="39" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H33" s="39" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I33" s="40" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J33" s="39">
         <v>1</v>
@@ -2635,14 +2633,14 @@
       </c>
       <c r="L33" s="63"/>
     </row>
-    <row r="34" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="53">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D34" s="37" t="s">
         <v>31</v>
@@ -2651,16 +2649,16 @@
         <v>57</v>
       </c>
       <c r="F34" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="G34" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="H34" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="I34" s="38" t="s">
         <v>146</v>
-      </c>
-      <c r="G34" s="38" t="s">
-        <v>185</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="I34" s="38" t="s">
-        <v>150</v>
       </c>
       <c r="J34" s="37">
         <v>1</v>
@@ -2670,17 +2668,17 @@
         <v>20</v>
       </c>
       <c r="L34" s="61" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="53">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D35" s="39" t="s">
         <v>32</v>
@@ -2689,16 +2687,16 @@
         <v>58</v>
       </c>
       <c r="F35" s="39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G35" s="39" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H35" s="39" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I35" s="40" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J35" s="39">
         <v>1</v>
@@ -2709,32 +2707,32 @@
       </c>
       <c r="L35" s="63"/>
     </row>
-    <row r="36" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="53">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D36" s="37" t="s">
         <v>33</v>
       </c>
       <c r="E36" s="38" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I36" s="38" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J36" s="37">
         <v>1</v>
@@ -2745,32 +2743,32 @@
       </c>
       <c r="L36" s="61"/>
     </row>
-    <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="53">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C37" s="39" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D37" s="39" t="s">
         <v>34</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>59</v>
+        <v>185</v>
       </c>
       <c r="F37" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="G37" s="40" t="s">
-        <v>98</v>
+        <v>186</v>
+      </c>
+      <c r="G37" s="39" t="s">
+        <v>187</v>
       </c>
       <c r="H37" s="39" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I37" s="40" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J37" s="39">
         <v>1</v>
@@ -2781,32 +2779,32 @@
       </c>
       <c r="L37" s="42"/>
     </row>
-    <row r="38" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="53">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D38" s="37" t="s">
         <v>35</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G38" s="38" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I38" s="38" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J38" s="37">
         <v>1</v>
@@ -2817,32 +2815,32 @@
       </c>
       <c r="L38" s="41"/>
     </row>
-    <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="53">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D39" s="39" t="s">
         <v>36</v>
       </c>
       <c r="E39" s="40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F39" s="39" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G39" s="40" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H39" s="39" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I39" s="40" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J39" s="39">
         <v>1</v>
@@ -2853,32 +2851,32 @@
       </c>
       <c r="L39" s="42"/>
     </row>
-    <row r="40" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="53">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D40" s="37" t="s">
         <v>37</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G40" s="38" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I40" s="38" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J40" s="37">
         <v>1</v>
@@ -2889,32 +2887,32 @@
       </c>
       <c r="L40" s="41"/>
     </row>
-    <row r="41" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="53">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C41" s="39" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D41" s="39" t="s">
         <v>38</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F41" s="39" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G41" s="40" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H41" s="39" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I41" s="40" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="J41" s="39">
         <v>1</v>
@@ -2925,32 +2923,32 @@
       </c>
       <c r="L41" s="42"/>
     </row>
-    <row r="42" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="53">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D42" s="37" t="s">
         <v>39</v>
       </c>
       <c r="E42" s="38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G42" s="38" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I42" s="38" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="J42" s="37">
         <v>1</v>
@@ -2961,7 +2959,7 @@
       </c>
       <c r="L42" s="41"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="32"/>
       <c r="C43" s="51"/>
@@ -2977,7 +2975,7 @@
       <c r="K43" s="36"/>
       <c r="L43" s="44"/>
     </row>
-    <row r="44" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="24"/>
       <c r="C44" s="52"/>

--- a/Deliverables/SM_Bottom Board/_BOM/Supplier BOM_Bottom (20 Boards).xlsx
+++ b/Deliverables/SM_Bottom Board/_BOM/Supplier BOM_Bottom (20 Boards).xlsx
@@ -1,35 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Bottom Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D5B6B3-999F-4D4F-B05A-0ABF0B447455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="180">
   <si>
     <t>Component list</t>
   </si>
@@ -46,18 +37,6 @@
     <t>#</t>
   </si>
   <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Bill of Materials for Project [SM_Bottom_Board.PrjPcb] (PCB Document : SM_Bottom_PCB.PcbDoc)</t>
-  </si>
-  <si>
-    <t>SM_Bottom_Board.PrjPcb</t>
-  </si>
-  <si>
     <t>None</t>
   </si>
   <si>
@@ -79,9 +58,6 @@
     <t>C18, C19</t>
   </si>
   <si>
-    <t>CF1</t>
-  </si>
-  <si>
     <t>D12</t>
   </si>
   <si>
@@ -196,18 +172,9 @@
     <t>RES SMD 1K 0.1W 0603  75 V, Thick Film</t>
   </si>
   <si>
-    <t>RES SMD 470 OHM 50 V, 0603 100 mW,  1%,</t>
-  </si>
-  <si>
     <t>Solder Bridge ON</t>
   </si>
   <si>
-    <t>IC MCU 32BIT 1MB FLASH 100LQFP</t>
-  </si>
-  <si>
-    <t>IC TRANSCEIVER 1/1 8SOIC</t>
-  </si>
-  <si>
     <t>IC BUF NON-INVERT 5.5V SOT23-5</t>
   </si>
   <si>
@@ -376,9 +343,6 @@
     <t>ECS International</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>4.7UF</t>
   </si>
   <si>
@@ -466,36 +430,18 @@
     <t>Quantity (20 Boards)</t>
   </si>
   <si>
-    <t>Remarks</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
     <t>TAJA105K016RNJ</t>
   </si>
   <si>
-    <t>UMK063CG100DTHF</t>
-  </si>
-  <si>
     <t>PESD2CAN,215</t>
   </si>
   <si>
     <t>Ferrite0603</t>
   </si>
   <si>
-    <t>MHT136CGCT</t>
-  </si>
-  <si>
-    <t>0201WMF8060TEE</t>
-  </si>
-  <si>
-    <t>CR0603-FX-57R6ELF</t>
-  </si>
-  <si>
-    <t>DO NOT MOUNT</t>
-  </si>
-  <si>
     <t>GT-TC025D-H0065-L1</t>
   </si>
   <si>
@@ -511,9 +457,6 @@
     <t>D1</t>
   </si>
   <si>
-    <t>C2, C3, C4, C5, C6, C7, C8, C9, C10, C11, C15, C32, C33, C34, C35, C36, C37, C50</t>
-  </si>
-  <si>
     <t>Rx1, Rx2</t>
   </si>
   <si>
@@ -523,98 +466,110 @@
     <t>100R</t>
   </si>
   <si>
-    <t>Quantity changed from 19/board to 18/board due to Encoder IC change</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">R6, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Rx3</t>
-    </r>
-  </si>
-  <si>
-    <t>Quantity changed from 1/board to 2/board due to Encoder IC change</t>
-  </si>
-  <si>
     <t>RES SMD 100 OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>Added due to Encoder IC</t>
-  </si>
-  <si>
     <t>Multiple options added for MCU</t>
   </si>
   <si>
-    <t>1uF 16V -55℃~+125℃ 11Ω ±10% CASE-A_3216</t>
-  </si>
-  <si>
-    <t>50V 10pF C0G ±0.5pF 0201 MLCC</t>
-  </si>
-  <si>
     <t>Nexperia</t>
   </si>
   <si>
-    <t>41V 5A 24V 26.2V Bidirectional</t>
-  </si>
-  <si>
-    <t>MEIHUA</t>
-  </si>
-  <si>
-    <t>UNI-ROYAL</t>
-  </si>
-  <si>
-    <t>50mW Thick Film Resistors 25V 806Ω 0201</t>
-  </si>
-  <si>
-    <t>BOURNS</t>
-  </si>
-  <si>
-    <t>100mW ±100ppm/℃ ±1% 57.6Ω 0603</t>
-  </si>
-  <si>
     <t>G-Switch</t>
   </si>
   <si>
-    <t>NO J pin 50mA 3mm 100MΩ 100000 12V</t>
-  </si>
-  <si>
-    <t>STM32F407VGT6</t>
-  </si>
-  <si>
     <t>Infineon</t>
   </si>
   <si>
-    <t>PG-DSO-8</t>
-  </si>
-  <si>
-    <t>PG-DSO-8 Position Sensor ROHS</t>
-  </si>
-  <si>
-    <t>LGA-14 Attitude Sensor/Gyroscope</t>
-  </si>
-  <si>
     <t>LGA-14</t>
   </si>
   <si>
     <t>LSM6DSLTR</t>
+  </si>
+  <si>
+    <t>C2, C3, C4, C5, C6, C7, C8, C9, C10, C11, C15, C32, C33, C34, C36, C37, C50, CF1</t>
+  </si>
+  <si>
+    <t>CAP TANT 1UF 10% 16V 1206</t>
+  </si>
+  <si>
+    <t>CAP CER 10PF 25V C0G 0201</t>
+  </si>
+  <si>
+    <t>CGA1A2C0G1E100D030BA</t>
+  </si>
+  <si>
+    <t>TVS DIODE 24VWM 41VC TO236AB</t>
+  </si>
+  <si>
+    <t>XZVG68W-2</t>
+  </si>
+  <si>
+    <t>SunLED</t>
+  </si>
+  <si>
+    <t>Res Thick Film 0201 806 Ohm 1% 1/20W ±200ppm/°C Molded SMD SMD Paper T/R</t>
+  </si>
+  <si>
+    <t>RMCF0201FT806R</t>
+  </si>
+  <si>
+    <t>Stackpole Electronics</t>
+  </si>
+  <si>
+    <t>R6, Rx3</t>
+  </si>
+  <si>
+    <t>RES SMD 470 OHM 50 V, 0603 100 mW,  1%,, RES SMD 470 OHM 50 V, 0603 100 mW,  1%, RC Series</t>
+  </si>
+  <si>
+    <t>RES SMD 57.6 OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RC0603FR-0757R6L</t>
+  </si>
+  <si>
+    <t>No NO J pin 50mA 3mm 100MΩ 100000 12V 250gf@±30gf 2.6mm -30℃~+85℃ 0.65mm Black Round Button Brick nogging SPST SMD Tactile Switches ROHS</t>
+  </si>
+  <si>
+    <t>IC MCU 32BIT 512KB FLASH 100LQFP</t>
+  </si>
+  <si>
+    <t>STM32F407VET6</t>
+  </si>
+  <si>
+    <t>IC TRANSCEIVER HALF 1/1 8SOIC</t>
+  </si>
+  <si>
+    <t>SENSOR ANGLE 360DEG SMD</t>
+  </si>
+  <si>
+    <t>QFN-24</t>
+  </si>
+  <si>
+    <t>IMUACCEL/GYROI2C/SPI14LGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value </t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>Bill of Materials for Project [SM_Bottom_Board.PrjPcb]</t>
+  </si>
+  <si>
+    <t>SM_Bottom_Board</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -748,7 +703,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -756,13 +710,29 @@
     <font>
       <strike/>
       <sz val="9"/>
-      <color rgb="FFC00000"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -793,26 +763,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="20">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -1031,26 +983,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -1060,18 +1038,18 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1086,7 +1064,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -1096,8 +1074,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1109,136 +1087,176 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1283,7 +1301,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1579,9 +1597,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -1607,87 +1625,87 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
     </row>
     <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
-      <c r="C2" s="46"/>
+      <c r="C2" s="39"/>
       <c r="D2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="10"/>
-      <c r="F2" s="54" t="s">
-        <v>7</v>
+      <c r="F2" s="45" t="s">
+        <v>178</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="43"/>
+      <c r="L2" s="38"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
-      <c r="C3" s="47"/>
+      <c r="C3" s="40"/>
       <c r="D3" s="12" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="12"/>
-      <c r="F3" s="55" t="s">
-        <v>8</v>
+      <c r="F3" s="46" t="s">
+        <v>179</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="73"/>
+      <c r="L3" s="51"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
-      <c r="C4" s="47"/>
+      <c r="C4" s="40"/>
       <c r="D4" s="12" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="12"/>
-      <c r="F4" s="56" t="s">
-        <v>8</v>
+      <c r="F4" s="47" t="s">
+        <v>179</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="74"/>
+      <c r="L4" s="52"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
-      <c r="C5" s="47"/>
+      <c r="C5" s="40"/>
       <c r="D5" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="57" t="s">
-        <v>9</v>
+      <c r="F5" s="48" t="s">
+        <v>5</v>
       </c>
       <c r="G5" s="14"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="74"/>
+      <c r="L5" s="52"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
-      <c r="C6" s="48"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="16"/>
@@ -1696,12 +1714,12 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="74"/>
+      <c r="L6" s="52"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
-      <c r="C7" s="49"/>
+      <c r="C7" s="42"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
@@ -1710,12 +1728,12 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="74"/>
+      <c r="L7" s="52"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
-      <c r="C8" s="50"/>
+      <c r="C8" s="43"/>
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
@@ -1724,7 +1742,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="74"/>
+      <c r="L8" s="52"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1732,1269 +1750,1223 @@
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>99</v>
+        <v>35</v>
+      </c>
+      <c r="F9" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>91</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>115</v>
+        <v>176</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="K9" s="29" t="s">
-        <v>144</v>
-      </c>
-      <c r="L9" s="31" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="53">
+      <c r="B10" s="54">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="37" t="s">
-        <v>130</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="I10" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="J10" s="37">
+      <c r="C10" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="56" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="I10" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" s="81">
         <v>1</v>
       </c>
-      <c r="K10" s="37">
+      <c r="K10" s="56">
         <f>J10*20</f>
         <v>20</v>
       </c>
-      <c r="L10" s="41"/>
-    </row>
-    <row r="11" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L10" s="85"/>
+    </row>
+    <row r="11" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="53">
-        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="58">
+        <f t="shared" ref="B11:B40" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="E11" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="I11" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="J11" s="65">
+      <c r="C11" s="59" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" s="60" t="s">
+        <v>155</v>
+      </c>
+      <c r="E11" s="60" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="61" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="I11" s="60" t="s">
+        <v>108</v>
+      </c>
+      <c r="J11" s="82">
         <v>18</v>
       </c>
-      <c r="K11" s="39">
-        <f>J11*20</f>
+      <c r="K11" s="60">
+        <f t="shared" ref="K11:K41" si="1">J11*20</f>
         <v>360</v>
       </c>
-      <c r="L11" s="68" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L11" s="60"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="53">
+      <c r="B12" s="54">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="37" t="s">
-        <v>130</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="F12" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="H12" s="37" t="s">
-        <v>101</v>
-      </c>
-      <c r="I12" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="J12" s="37">
+      <c r="C12" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="56" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="G12" s="56" t="s">
+        <v>137</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="J12" s="81">
         <v>1</v>
       </c>
-      <c r="K12" s="37">
-        <f t="shared" ref="K12:K30" si="1">J12*20</f>
+      <c r="K12" s="56">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L12" s="61"/>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L12" s="56"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="53">
+      <c r="B13" s="58">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="I13" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="J13" s="39">
+      <c r="C13" s="59" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="61" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="60" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="I13" s="60" t="s">
+        <v>110</v>
+      </c>
+      <c r="J13" s="82">
         <v>2</v>
       </c>
-      <c r="K13" s="39">
+      <c r="K13" s="60">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L13" s="42"/>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L13" s="60"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="53">
+      <c r="B14" s="54">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="37" t="s">
-        <v>130</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="I14" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="J14" s="37">
+      <c r="C14" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="D14" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="I14" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="J14" s="81">
         <v>2</v>
       </c>
-      <c r="K14" s="37">
+      <c r="K14" s="56">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L14" s="41"/>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L14" s="56"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="53">
+      <c r="B15" s="58">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="40" t="s">
-        <v>171</v>
-      </c>
-      <c r="F15" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="H15" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="I15" s="40" t="s">
+      <c r="C15" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="J15" s="39">
+      <c r="D15" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="60" t="s">
+        <v>157</v>
+      </c>
+      <c r="F15" s="61" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="I15" s="60" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" s="82">
         <v>2</v>
       </c>
-      <c r="K15" s="39">
+      <c r="K15" s="60">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L15" s="42"/>
-    </row>
-    <row r="16" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L15" s="60"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="53">
+      <c r="B16" s="58">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="D16" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="H16" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="I16" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="J16" s="39">
+      <c r="C16" s="63" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="G16" s="64" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="I16" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="J16" s="37">
         <v>1</v>
       </c>
-      <c r="K16" s="39">
+      <c r="K16" s="34">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L16" s="42"/>
-    </row>
-    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L16" s="34"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="53">
+      <c r="B17" s="54">
         <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
-      <c r="C17" s="37" t="s">
-        <v>131</v>
-      </c>
-      <c r="D17" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="F17" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="G17" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="H17" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="I17" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="J17" s="62">
+      <c r="C17" s="65" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="J17" s="36">
         <v>1</v>
       </c>
-      <c r="K17" s="37">
+      <c r="K17" s="32">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L17" s="61"/>
-    </row>
-    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L17" s="32"/>
+    </row>
+    <row r="18" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="53">
+      <c r="B18" s="58">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="39" t="s">
-        <v>131</v>
-      </c>
-      <c r="D18" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="H18" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="I18" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="J18" s="39">
+      <c r="C18" s="63" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="G18" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="I18" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="J18" s="37">
+        <v>4</v>
+      </c>
+      <c r="K18" s="34">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="L18" s="34"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="54">
+        <f>ROW(B19) - ROW($B$9)</f>
+        <v>10</v>
+      </c>
+      <c r="C19" s="66" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="G19" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="I19" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="J19" s="36">
         <v>1</v>
       </c>
-      <c r="K18" s="39">
+      <c r="K19" s="32">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L18" s="42"/>
-    </row>
-    <row r="19" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="53">
-        <f>ROW(B19) - ROW($B$9)</f>
-        <v>10</v>
-      </c>
-      <c r="C19" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="G19" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="H19" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="I19" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="J19" s="37">
-        <v>4</v>
-      </c>
-      <c r="K19" s="37">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="L19" s="41"/>
-    </row>
-    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L19" s="32"/>
+    </row>
+    <row r="20" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="53">
+      <c r="B20" s="58">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="D20" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="G20" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="H20" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="I20" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="J20" s="39">
+      <c r="C20" s="63" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="H20" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="I20" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="J20" s="37">
         <v>1</v>
       </c>
-      <c r="K20" s="39">
+      <c r="K20" s="34">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L20" s="42"/>
-    </row>
-    <row r="21" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L20" s="34"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="53">
+      <c r="B21" s="54">
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="D21" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="H21" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="I21" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="J21" s="37">
+      <c r="C21" s="66" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="H21" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="I21" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="J21" s="36">
         <v>1</v>
       </c>
-      <c r="K21" s="37">
+      <c r="K21" s="32">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L21" s="41"/>
-    </row>
-    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L21" s="32"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="53">
+      <c r="B22" s="58">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="D22" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="F22" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="G22" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="H22" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="I22" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="J22" s="39">
+      <c r="C22" s="63" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="H22" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="I22" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="J22" s="37">
         <v>1</v>
       </c>
-      <c r="K22" s="39">
+      <c r="K22" s="34">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L22" s="42"/>
-    </row>
-    <row r="23" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L22" s="34"/>
+    </row>
+    <row r="23" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="53">
+      <c r="B23" s="54">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="D23" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="F23" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="G23" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H23" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="I23" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="J23" s="37">
+      <c r="C23" s="66" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="I23" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="J23" s="36">
+        <v>2</v>
+      </c>
+      <c r="K23" s="32">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="L23" s="32"/>
+    </row>
+    <row r="24" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="58">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C24" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H24" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="I24" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="J24" s="37">
+        <v>40</v>
+      </c>
+      <c r="K24" s="34">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="L24" s="34"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="54">
+        <f>ROW(B25) - ROW($B$9)</f>
+        <v>16</v>
+      </c>
+      <c r="C25" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="I25" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="J25" s="36">
+        <v>7</v>
+      </c>
+      <c r="K25" s="32">
+        <f t="shared" si="1"/>
+        <v>140</v>
+      </c>
+      <c r="L25" s="32"/>
+    </row>
+    <row r="26" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="58">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C26" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="D26" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="F26" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="G26" s="68" t="s">
+        <v>163</v>
+      </c>
+      <c r="H26" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="I26" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="J26" s="37">
         <v>1</v>
       </c>
-      <c r="K23" s="37">
+      <c r="K26" s="34">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L23" s="41"/>
-    </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="53">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>136</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="F24" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="G24" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="H24" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="I24" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="J24" s="39">
+      <c r="L26" s="34"/>
+    </row>
+    <row r="27" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="54">
+        <f>ROW(B27) - ROW($B$9)</f>
+        <v>18</v>
+      </c>
+      <c r="C27" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="H27" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="J27" s="36">
         <v>2</v>
       </c>
-      <c r="K24" s="39">
+      <c r="K27" s="32">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L24" s="42"/>
-    </row>
-    <row r="25" spans="1:12" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="53">
-        <f>ROW(B25) - ROW($B$9)</f>
-        <v>16</v>
-      </c>
-      <c r="C25" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="D25" s="37" t="s">
+      <c r="L27" s="32"/>
+    </row>
+    <row r="28" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="58">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C28" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="E28" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="F28" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="H28" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="I28" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="J28" s="37">
+        <v>2</v>
+      </c>
+      <c r="K28" s="34">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="L28" s="34"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="54">
+        <f>ROW(B29) - ROW($B$9)</f>
+        <v>20</v>
+      </c>
+      <c r="C29" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="67" t="s">
+        <v>168</v>
+      </c>
+      <c r="H29" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="I29" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="J29" s="36">
+        <v>2</v>
+      </c>
+      <c r="K29" s="32">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="L29" s="32"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="58">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C30" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E30" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="F30" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="H30" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="I30" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="J30" s="37">
+        <v>2</v>
+      </c>
+      <c r="K30" s="34">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="L30" s="34"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="54">
+        <f>ROW(B31) - ROW($B$9)</f>
+        <v>22</v>
+      </c>
+      <c r="C31" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="F25" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="G25" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="I25" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="J25" s="37">
-        <v>40</v>
-      </c>
-      <c r="K25" s="37">
+      <c r="E31" s="67" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="G31" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="H31" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="I31" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="J31" s="83">
+        <v>8</v>
+      </c>
+      <c r="K31" s="67">
         <f t="shared" si="1"/>
-        <v>800</v>
-      </c>
-      <c r="L25" s="41"/>
-    </row>
-    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1"/>
-      <c r="B26" s="53">
+        <v>160</v>
+      </c>
+      <c r="L31" s="67"/>
+    </row>
+    <row r="32" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="58">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="D26" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="63" t="s">
+        <v>129</v>
+      </c>
+      <c r="D32" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="E26" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="F26" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="H26" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="I26" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="J26" s="39">
-        <v>7</v>
-      </c>
-      <c r="K26" s="39">
-        <f t="shared" si="1"/>
+      <c r="E32" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="F32" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="G32" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="L26" s="42"/>
-    </row>
-    <row r="27" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1"/>
-      <c r="B27" s="53">
-        <f>ROW(B27) - ROW($B$9)</f>
-        <v>18</v>
-      </c>
-      <c r="C27" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="D27" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="F27" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="G27" s="38" t="s">
-        <v>152</v>
-      </c>
-      <c r="H27" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="I27" s="38" t="s">
-        <v>124</v>
-      </c>
-      <c r="J27" s="37">
+      <c r="H32" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="I32" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="J32" s="37">
         <v>1</v>
       </c>
-      <c r="K27" s="37">
+      <c r="K32" s="34">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L27" s="41"/>
-    </row>
-    <row r="28" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1"/>
-      <c r="B28" s="53">
+      <c r="L32" s="34"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="54">
+        <f>ROW(B33) - ROW($B$9)</f>
+        <v>24</v>
+      </c>
+      <c r="C33" s="66" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="F33" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G33" s="67" t="s">
+        <v>171</v>
+      </c>
+      <c r="H33" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="I33" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="J33" s="36">
+        <v>1</v>
+      </c>
+      <c r="K33" s="32">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="L33" s="49" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="58">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="D28" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="63" t="s">
+        <v>130</v>
+      </c>
+      <c r="D34" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="E28" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="F28" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="H28" s="39" t="s">
+      <c r="E34" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="F34" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G34" s="64" t="s">
+        <v>141</v>
+      </c>
+      <c r="H34" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="I28" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="J28" s="39">
-        <v>2</v>
-      </c>
-      <c r="K28" s="39">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="L28" s="42"/>
-    </row>
-    <row r="29" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1"/>
-      <c r="B29" s="53">
-        <f>ROW(B29) - ROW($B$9)</f>
-        <v>20</v>
-      </c>
-      <c r="C29" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="D29" s="66" t="s">
-        <v>165</v>
-      </c>
-      <c r="E29" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="G29" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="H29" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="I29" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="J29" s="67">
-        <v>2</v>
-      </c>
-      <c r="K29" s="37">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="L29" s="61" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1"/>
-      <c r="B30" s="53">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C30" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="D30" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="E30" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="F30" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="G30" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="H30" s="39" t="s">
-        <v>177</v>
-      </c>
-      <c r="I30" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="J30" s="39">
-        <v>2</v>
-      </c>
-      <c r="K30" s="39">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="L30" s="42"/>
-    </row>
-    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1"/>
-      <c r="B31" s="53">
-        <v>22</v>
-      </c>
-      <c r="C31" s="69" t="s">
-        <v>137</v>
-      </c>
-      <c r="D31" s="64" t="s">
-        <v>161</v>
-      </c>
-      <c r="E31" s="70" t="s">
-        <v>167</v>
-      </c>
-      <c r="F31" s="64" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="70" t="s">
-        <v>162</v>
-      </c>
-      <c r="H31" s="64" t="s">
-        <v>103</v>
-      </c>
-      <c r="I31" s="70" t="s">
-        <v>163</v>
-      </c>
-      <c r="J31" s="64">
-        <v>2</v>
-      </c>
-      <c r="K31" s="64">
-        <f t="shared" ref="K31:K42" si="2">J31*20</f>
-        <v>40</v>
-      </c>
-      <c r="L31" s="71" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1"/>
-      <c r="B32" s="53">
-        <f>ROW(B32) - ROW($B$9)</f>
-        <v>23</v>
-      </c>
-      <c r="C32" s="58" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" s="58" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32" s="59" t="s">
-        <v>56</v>
-      </c>
-      <c r="F32" s="58" t="s">
-        <v>77</v>
-      </c>
-      <c r="G32" s="59" t="s">
-        <v>146</v>
-      </c>
-      <c r="H32" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="I32" s="59" t="s">
-        <v>146</v>
-      </c>
-      <c r="J32" s="58">
-        <v>8</v>
-      </c>
-      <c r="K32" s="58">
-        <f t="shared" si="2"/>
-        <v>160</v>
-      </c>
-      <c r="L32" s="60" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1"/>
-      <c r="B33" s="53">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="C33" s="39" t="s">
-        <v>138</v>
-      </c>
-      <c r="D33" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="E33" s="40" t="s">
-        <v>180</v>
-      </c>
-      <c r="F33" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="G33" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="H33" s="39" t="s">
-        <v>179</v>
-      </c>
-      <c r="I33" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="J33" s="39">
-        <v>1</v>
-      </c>
-      <c r="K33" s="39">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="L33" s="63"/>
-    </row>
-    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1"/>
-      <c r="B34" s="53">
-        <f>ROW(B34) - ROW($B$9)</f>
-        <v>25</v>
-      </c>
-      <c r="C34" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="D34" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="F34" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="G34" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="I34" s="38" t="s">
-        <v>146</v>
+      <c r="I34" s="34" t="s">
+        <v>136</v>
       </c>
       <c r="J34" s="37">
         <v>1</v>
       </c>
-      <c r="K34" s="37">
-        <f t="shared" si="2"/>
+      <c r="K34" s="34">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L34" s="61" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L34" s="34"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="53">
+      <c r="B35" s="54">
+        <f>ROW(B35) - ROW($B$9)</f>
+        <v>26</v>
+      </c>
+      <c r="C35" s="66" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="F35" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="G35" s="67" t="s">
+        <v>142</v>
+      </c>
+      <c r="H35" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="I35" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="J35" s="36">
+        <v>1</v>
+      </c>
+      <c r="K35" s="32">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="L35" s="32"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="C35" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="D35" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="F35" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="G35" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="H35" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="I35" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="J35" s="39">
-        <v>1</v>
-      </c>
-      <c r="K35" s="39">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="L35" s="63"/>
-    </row>
-    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1"/>
-      <c r="B36" s="53">
-        <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="D36" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E36" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>183</v>
-      </c>
-      <c r="G36" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="H36" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="I36" s="38" t="s">
-        <v>146</v>
+      <c r="C36" s="63" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="F36" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="G36" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="H36" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="I36" s="34" t="s">
+        <v>136</v>
       </c>
       <c r="J36" s="37">
         <v>1</v>
       </c>
-      <c r="K36" s="37">
-        <f t="shared" si="2"/>
+      <c r="K36" s="34">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L36" s="61"/>
-    </row>
-    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L36" s="34"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="53">
+      <c r="B37" s="54">
+        <f>ROW(B37) - ROW($B$9)</f>
+        <v>28</v>
+      </c>
+      <c r="C37" s="66" t="s">
+        <v>130</v>
+      </c>
+      <c r="D37" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="F37" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="G37" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="H37" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="I37" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="J37" s="36">
+        <v>1</v>
+      </c>
+      <c r="K37" s="32">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="L37" s="32"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="C37" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="D37" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="E37" s="40" t="s">
-        <v>185</v>
-      </c>
-      <c r="F37" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="G37" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="H37" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="I37" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="J37" s="39">
-        <v>1</v>
-      </c>
-      <c r="K37" s="39">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="L37" s="42"/>
-    </row>
-    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1"/>
-      <c r="B38" s="53">
-        <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="D38" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="E38" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="F38" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="G38" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="H38" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="I38" s="38" t="s">
-        <v>146</v>
+      <c r="C38" s="63" t="s">
+        <v>130</v>
+      </c>
+      <c r="D38" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="F38" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="G38" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="H38" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="I38" s="34" t="s">
+        <v>136</v>
       </c>
       <c r="J38" s="37">
         <v>1</v>
       </c>
-      <c r="K38" s="37">
-        <f t="shared" si="2"/>
+      <c r="K38" s="34">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L38" s="41"/>
-    </row>
-    <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L38" s="34"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="53">
+      <c r="B39" s="54">
+        <f>ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="66" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="G39" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="H39" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="I39" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="J39" s="36">
+        <v>1</v>
+      </c>
+      <c r="K39" s="32">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="L39" s="32"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="58">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="C39" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="D39" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="E39" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="F39" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="G39" s="40" t="s">
-        <v>97</v>
-      </c>
-      <c r="H39" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="I39" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="J39" s="39">
-        <v>1</v>
-      </c>
-      <c r="K39" s="39">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="L39" s="42"/>
-    </row>
-    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="53">
-        <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="E40" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="G40" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="H40" s="37" t="s">
+      <c r="C40" s="63" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="E40" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="F40" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="G40" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="H40" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="I40" s="38" t="s">
-        <v>146</v>
+      <c r="I40" s="34" t="s">
+        <v>119</v>
       </c>
       <c r="J40" s="37">
         <v>1</v>
       </c>
-      <c r="K40" s="37">
-        <f t="shared" si="2"/>
+      <c r="K40" s="34">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L40" s="41"/>
+      <c r="L40" s="34"/>
     </row>
     <row r="41" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="53">
-        <f t="shared" si="0"/>
+      <c r="B41" s="71">
+        <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="39" t="s">
-        <v>140</v>
-      </c>
-      <c r="D41" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="E41" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F41" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="G41" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="H41" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="I41" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="J41" s="39">
+      <c r="C41" s="72" t="s">
+        <v>131</v>
+      </c>
+      <c r="D41" s="73" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" s="73" t="s">
+        <v>55</v>
+      </c>
+      <c r="F41" s="74" t="s">
+        <v>132</v>
+      </c>
+      <c r="G41" s="73" t="s">
+        <v>75</v>
+      </c>
+      <c r="H41" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="I41" s="73" t="s">
+        <v>143</v>
+      </c>
+      <c r="J41" s="84">
         <v>1</v>
       </c>
-      <c r="K41" s="39">
-        <f t="shared" si="2"/>
+      <c r="K41" s="73">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L41" s="42"/>
-    </row>
-    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L41" s="73"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="53">
-        <f>ROW(B42) - ROW($B$9)</f>
-        <v>33</v>
-      </c>
-      <c r="C42" s="37" t="s">
-        <v>140</v>
-      </c>
-      <c r="D42" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="E42" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="F42" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="G42" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="H42" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="I42" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="J42" s="37">
-        <v>1</v>
-      </c>
-      <c r="K42" s="37">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="L42" s="41"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B42" s="75"/>
+      <c r="C42" s="76"/>
+      <c r="D42" s="77"/>
+      <c r="E42" s="78"/>
+      <c r="F42" s="79"/>
+      <c r="G42" s="80"/>
+      <c r="H42" s="79"/>
+      <c r="I42" s="80"/>
+      <c r="J42" s="80"/>
+      <c r="K42" s="80"/>
+      <c r="L42" s="86"/>
+    </row>
+    <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
-      <c r="B43" s="32"/>
-      <c r="C43" s="51"/>
-      <c r="D43" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="E43" s="34"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="35"/>
-      <c r="I43" s="36"/>
-      <c r="J43" s="36"/>
-      <c r="K43" s="36"/>
-      <c r="L43" s="44"/>
-    </row>
-    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1"/>
-      <c r="B44" s="24"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="45"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="87"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="L3:L8"/>
+    <mergeCell ref="L42:L43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Deliverables/SM_Bottom Board/_BOM/Supplier BOM_Bottom (20 Boards).xlsx
+++ b/Deliverables/SM_Bottom Board/_BOM/Supplier BOM_Bottom (20 Boards).xlsx
@@ -1,26 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Bottom Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D5B6B3-999F-4D4F-B05A-0ABF0B447455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="179">
   <si>
     <t>Component list</t>
   </si>
@@ -469,9 +468,6 @@
     <t>RES SMD 100 OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>Multiple options added for MCU</t>
-  </si>
-  <si>
     <t>Nexperia</t>
   </si>
   <si>
@@ -496,24 +492,15 @@
     <t>CAP CER 10PF 25V C0G 0201</t>
   </si>
   <si>
-    <t>CGA1A2C0G1E100D030BA</t>
-  </si>
-  <si>
     <t>TVS DIODE 24VWM 41VC TO236AB</t>
   </si>
   <si>
-    <t>XZVG68W-2</t>
-  </si>
-  <si>
     <t>SunLED</t>
   </si>
   <si>
     <t>Res Thick Film 0201 806 Ohm 1% 1/20W ±200ppm/°C Molded SMD SMD Paper T/R</t>
   </si>
   <si>
-    <t>RMCF0201FT806R</t>
-  </si>
-  <si>
     <t>Stackpole Electronics</t>
   </si>
   <si>
@@ -526,9 +513,6 @@
     <t>RES SMD 57.6 OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>RC0603FR-0757R6L</t>
-  </si>
-  <si>
     <t>No NO J pin 50mA 3mm 100MΩ 100000 12V 250gf@±30gf 2.6mm -30℃~+85℃ 0.65mm Black Round Button Brick nogging SPST SMD Tactile Switches ROHS</t>
   </si>
   <si>
@@ -560,12 +544,24 @@
   </si>
   <si>
     <t>SM_Bottom_Board</t>
+  </si>
+  <si>
+    <t>UMK063CG100DTHF</t>
+  </si>
+  <si>
+    <t>MHT136CGCT</t>
+  </si>
+  <si>
+    <t>0201WMF8060TEE</t>
+  </si>
+  <si>
+    <t>CR0603-FX-57R6ELF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
@@ -1013,7 +1009,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1142,15 +1138,6 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1178,9 +1165,6 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1194,9 +1178,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1250,6 +1231,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1597,7 +1590,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:L43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1625,10 +1618,10 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
     </row>
     <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1639,7 +1632,7 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="45" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
@@ -1657,14 +1650,14 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="46" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="51"/>
+      <c r="L3" s="83"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1675,14 +1668,14 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="47" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="52"/>
+      <c r="L4" s="84"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1700,7 +1693,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="52"/>
+      <c r="L5" s="84"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1714,7 +1707,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="52"/>
+      <c r="L6" s="84"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1728,7 +1721,7 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="52"/>
+      <c r="L7" s="84"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1742,7 +1735,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="52"/>
+      <c r="L8" s="84"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1758,7 +1751,7 @@
       <c r="E9" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="53" t="s">
+      <c r="F9" s="50" t="s">
         <v>56</v>
       </c>
       <c r="G9" s="29" t="s">
@@ -1768,7 +1761,7 @@
         <v>91</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="J9" s="29" t="s">
         <v>120</v>
@@ -1777,248 +1770,248 @@
         <v>135</v>
       </c>
       <c r="L9" s="29" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="54">
+      <c r="B10" s="51">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="D10" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="56" t="s">
+      <c r="E10" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="57" t="s">
+      <c r="F10" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="56" t="s">
+      <c r="G10" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="H10" s="57" t="s">
+      <c r="H10" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="I10" s="56" t="s">
+      <c r="I10" s="53" t="s">
         <v>107</v>
       </c>
-      <c r="J10" s="81">
+      <c r="J10" s="76">
         <v>1</v>
       </c>
-      <c r="K10" s="56">
+      <c r="K10" s="53">
         <f>J10*20</f>
         <v>20</v>
       </c>
-      <c r="L10" s="85"/>
+      <c r="L10" s="80"/>
     </row>
     <row r="11" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="58">
+      <c r="B11" s="55">
         <f t="shared" ref="B11:B40" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="60" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" s="60" t="s">
+      <c r="D11" s="57" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="60" t="s">
+      <c r="G11" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="H11" s="61" t="s">
+      <c r="H11" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="I11" s="60" t="s">
+      <c r="I11" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="J11" s="82">
+      <c r="J11" s="77">
         <v>18</v>
       </c>
-      <c r="K11" s="60">
+      <c r="K11" s="57">
         <f t="shared" ref="K11:K41" si="1">J11*20</f>
         <v>360</v>
       </c>
-      <c r="L11" s="60"/>
+      <c r="L11" s="57"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="54">
+      <c r="B12" s="51">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="55" t="s">
+      <c r="C12" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="D12" s="56" t="s">
+      <c r="D12" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="56" t="s">
-        <v>156</v>
-      </c>
-      <c r="F12" s="57" t="s">
+      <c r="E12" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" s="54" t="s">
         <v>132</v>
       </c>
-      <c r="G12" s="56" t="s">
+      <c r="G12" s="53" t="s">
         <v>137</v>
       </c>
-      <c r="H12" s="57" t="s">
+      <c r="H12" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="I12" s="56" t="s">
+      <c r="I12" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="J12" s="81">
+      <c r="J12" s="76">
         <v>1</v>
       </c>
-      <c r="K12" s="56">
+      <c r="K12" s="53">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L12" s="56"/>
+      <c r="L12" s="53"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="58">
+      <c r="B13" s="55">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="D13" s="60" t="s">
+      <c r="D13" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="60" t="s">
+      <c r="E13" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="61" t="s">
+      <c r="F13" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="G13" s="60" t="s">
+      <c r="G13" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="H13" s="61" t="s">
+      <c r="H13" s="58" t="s">
         <v>94</v>
       </c>
-      <c r="I13" s="60" t="s">
+      <c r="I13" s="57" t="s">
         <v>110</v>
       </c>
-      <c r="J13" s="82">
+      <c r="J13" s="77">
         <v>2</v>
       </c>
-      <c r="K13" s="60">
+      <c r="K13" s="57">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L13" s="60"/>
+      <c r="L13" s="57"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="54">
+      <c r="B14" s="51">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="D14" s="56" t="s">
+      <c r="D14" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="56" t="s">
+      <c r="E14" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="57" t="s">
+      <c r="F14" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="G14" s="56" t="s">
+      <c r="G14" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="H14" s="57" t="s">
+      <c r="H14" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="I14" s="56" t="s">
+      <c r="I14" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="J14" s="81">
+      <c r="J14" s="76">
         <v>2</v>
       </c>
-      <c r="K14" s="56">
+      <c r="K14" s="53">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L14" s="56"/>
+      <c r="L14" s="53"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="58">
+      <c r="B15" s="55">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="D15" s="60" t="s">
+      <c r="D15" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="60" t="s">
-        <v>157</v>
-      </c>
-      <c r="F15" s="61" t="s">
+      <c r="E15" s="57" t="s">
+        <v>156</v>
+      </c>
+      <c r="F15" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="G15" s="62" t="s">
-        <v>158</v>
-      </c>
-      <c r="H15" s="61" t="s">
+      <c r="G15" s="57" t="s">
+        <v>175</v>
+      </c>
+      <c r="H15" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="I15" s="60" t="s">
+      <c r="I15" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="J15" s="82">
+      <c r="J15" s="77">
         <v>2</v>
       </c>
-      <c r="K15" s="60">
+      <c r="K15" s="57">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="L15" s="60"/>
+      <c r="L15" s="57"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="58">
+      <c r="B16" s="55">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="63" t="s">
+      <c r="C16" s="59" t="s">
         <v>122</v>
       </c>
       <c r="D16" s="34" t="s">
         <v>144</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F16" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="G16" s="64" t="s">
+      <c r="G16" s="60" t="s">
         <v>138</v>
       </c>
       <c r="H16" s="35" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I16" s="34" t="s">
         <v>136</v>
@@ -2034,11 +2027,11 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="54">
+      <c r="B17" s="51">
         <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
-      <c r="C17" s="65" t="s">
+      <c r="C17" s="61" t="s">
         <v>122</v>
       </c>
       <c r="D17" s="32" t="s">
@@ -2070,11 +2063,11 @@
     </row>
     <row r="18" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="58">
+      <c r="B18" s="55">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="59" t="s">
         <v>123</v>
       </c>
       <c r="D18" s="34" t="s">
@@ -2106,11 +2099,11 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="54">
+      <c r="B19" s="51">
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="66" t="s">
+      <c r="C19" s="62" t="s">
         <v>124</v>
       </c>
       <c r="D19" s="32" t="s">
@@ -2142,11 +2135,11 @@
     </row>
     <row r="20" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="58">
+      <c r="B20" s="55">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="63" t="s">
+      <c r="C20" s="59" t="s">
         <v>123</v>
       </c>
       <c r="D20" s="34" t="s">
@@ -2178,11 +2171,11 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="54">
+      <c r="B21" s="51">
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="66" t="s">
+      <c r="C21" s="62" t="s">
         <v>125</v>
       </c>
       <c r="D21" s="32" t="s">
@@ -2194,11 +2187,11 @@
       <c r="F21" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="G21" s="67" t="s">
-        <v>160</v>
+      <c r="G21" s="32" t="s">
+        <v>176</v>
       </c>
       <c r="H21" s="33" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I21" s="32" t="s">
         <v>136</v>
@@ -2214,11 +2207,11 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="58">
+      <c r="B22" s="55">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="63" t="s">
+      <c r="C22" s="59" t="s">
         <v>126</v>
       </c>
       <c r="D22" s="34" t="s">
@@ -2250,11 +2243,11 @@
     </row>
     <row r="23" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="54">
+      <c r="B23" s="51">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="66" t="s">
+      <c r="C23" s="62" t="s">
         <v>127</v>
       </c>
       <c r="D23" s="32" t="s">
@@ -2286,11 +2279,11 @@
     </row>
     <row r="24" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="58">
+      <c r="B24" s="55">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="63" t="s">
+      <c r="C24" s="59" t="s">
         <v>128</v>
       </c>
       <c r="D24" s="34" t="s">
@@ -2322,11 +2315,11 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="54">
+      <c r="B25" s="51">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="66" t="s">
+      <c r="C25" s="62" t="s">
         <v>128</v>
       </c>
       <c r="D25" s="32" t="s">
@@ -2358,27 +2351,27 @@
     </row>
     <row r="26" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="58">
+      <c r="B26" s="55">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="63" t="s">
+      <c r="C26" s="59" t="s">
         <v>128</v>
       </c>
       <c r="D26" s="34" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="34" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F26" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="G26" s="68" t="s">
-        <v>163</v>
+      <c r="G26" s="34" t="s">
+        <v>177</v>
       </c>
       <c r="H26" s="35" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I26" s="34" t="s">
         <v>115</v>
@@ -2394,11 +2387,11 @@
     </row>
     <row r="27" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="54">
+      <c r="B27" s="51">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="66" t="s">
+      <c r="C27" s="62" t="s">
         <v>128</v>
       </c>
       <c r="D27" s="32" t="s">
@@ -2430,18 +2423,18 @@
     </row>
     <row r="28" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="58">
+      <c r="B28" s="55">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="63" t="s">
+      <c r="C28" s="59" t="s">
         <v>128</v>
       </c>
       <c r="D28" s="34" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E28" s="34" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F28" s="35" t="s">
         <v>68</v>
@@ -2466,24 +2459,24 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="54">
+      <c r="B29" s="51">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="66" t="s">
+      <c r="C29" s="62" t="s">
         <v>128</v>
       </c>
       <c r="D29" s="32" t="s">
         <v>23</v>
       </c>
       <c r="E29" s="32" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F29" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="G29" s="67" t="s">
-        <v>168</v>
+      <c r="G29" s="32" t="s">
+        <v>178</v>
       </c>
       <c r="H29" s="33" t="s">
         <v>95</v>
@@ -2502,11 +2495,11 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="58">
+      <c r="B30" s="55">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="63" t="s">
+      <c r="C30" s="59" t="s">
         <v>128</v>
       </c>
       <c r="D30" s="34" t="s">
@@ -2538,54 +2531,54 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="54">
+      <c r="B31" s="51">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="69" t="s">
+      <c r="C31" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="D31" s="67" t="s">
+      <c r="D31" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="67" t="s">
+      <c r="E31" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="F31" s="70" t="s">
+      <c r="F31" s="65" t="s">
         <v>136</v>
       </c>
-      <c r="G31" s="67" t="s">
+      <c r="G31" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="H31" s="70" t="s">
+      <c r="H31" s="65" t="s">
         <v>136</v>
       </c>
-      <c r="I31" s="67" t="s">
+      <c r="I31" s="63" t="s">
         <v>136</v>
       </c>
-      <c r="J31" s="83">
+      <c r="J31" s="78">
         <v>8</v>
       </c>
-      <c r="K31" s="67">
+      <c r="K31" s="63">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="L31" s="67"/>
+      <c r="L31" s="63"/>
     </row>
     <row r="32" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="58">
+      <c r="B32" s="55">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="63" t="s">
+      <c r="C32" s="59" t="s">
         <v>129</v>
       </c>
       <c r="D32" s="34" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="34" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="F32" s="35" t="s">
         <v>132</v>
@@ -2594,7 +2587,7 @@
         <v>140</v>
       </c>
       <c r="H32" s="35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I32" s="34" t="s">
         <v>136</v>
@@ -2610,24 +2603,24 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="54">
+      <c r="B33" s="51">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="66" t="s">
+      <c r="C33" s="62" t="s">
         <v>130</v>
       </c>
       <c r="D33" s="32" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F33" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="G33" s="67" t="s">
-        <v>171</v>
+      <c r="G33" s="81" t="s">
+        <v>166</v>
       </c>
       <c r="H33" s="33" t="s">
         <v>102</v>
@@ -2642,29 +2635,27 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L33" s="49" t="s">
-        <v>149</v>
-      </c>
+      <c r="L33" s="49"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="58">
+      <c r="B34" s="55">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="63" t="s">
+      <c r="C34" s="59" t="s">
         <v>130</v>
       </c>
       <c r="D34" s="34" t="s">
         <v>27</v>
       </c>
       <c r="E34" s="34" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F34" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="G34" s="64" t="s">
+      <c r="G34" s="60" t="s">
         <v>141</v>
       </c>
       <c r="H34" s="35" t="s">
@@ -2684,27 +2675,27 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="54">
+      <c r="B35" s="51">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="66" t="s">
+      <c r="C35" s="62" t="s">
         <v>130</v>
       </c>
       <c r="D35" s="32" t="s">
         <v>28</v>
       </c>
       <c r="E35" s="32" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F35" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="G35" s="67" t="s">
+        <v>169</v>
+      </c>
+      <c r="G35" s="32" t="s">
         <v>142</v>
       </c>
       <c r="H35" s="33" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I35" s="32" t="s">
         <v>136</v>
@@ -2720,24 +2711,24 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="58">
+      <c r="B36" s="55">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="63" t="s">
+      <c r="C36" s="59" t="s">
         <v>130</v>
       </c>
       <c r="D36" s="34" t="s">
         <v>29</v>
       </c>
       <c r="E36" s="34" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F36" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="G36" s="34" t="s">
         <v>153</v>
-      </c>
-      <c r="G36" s="68" t="s">
-        <v>154</v>
       </c>
       <c r="H36" s="35" t="s">
         <v>102</v>
@@ -2756,11 +2747,11 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="54">
+      <c r="B37" s="51">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="66" t="s">
+      <c r="C37" s="62" t="s">
         <v>130</v>
       </c>
       <c r="D37" s="32" t="s">
@@ -2792,11 +2783,11 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="58">
+      <c r="B38" s="55">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="63" t="s">
+      <c r="C38" s="59" t="s">
         <v>130</v>
       </c>
       <c r="D38" s="34" t="s">
@@ -2828,11 +2819,11 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="54">
+      <c r="B39" s="51">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="66" t="s">
+      <c r="C39" s="62" t="s">
         <v>130</v>
       </c>
       <c r="D39" s="32" t="s">
@@ -2864,11 +2855,11 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="58">
+      <c r="B40" s="55">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="63" t="s">
+      <c r="C40" s="59" t="s">
         <v>131</v>
       </c>
       <c r="D40" s="34" t="s">
@@ -2900,53 +2891,53 @@
     </row>
     <row r="41" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="71">
+      <c r="B41" s="66">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="72" t="s">
+      <c r="C41" s="67" t="s">
         <v>131</v>
       </c>
-      <c r="D41" s="73" t="s">
+      <c r="D41" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="E41" s="73" t="s">
+      <c r="E41" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="74" t="s">
+      <c r="F41" s="69" t="s">
         <v>132</v>
       </c>
-      <c r="G41" s="73" t="s">
+      <c r="G41" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="H41" s="74" t="s">
+      <c r="H41" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="I41" s="73" t="s">
+      <c r="I41" s="68" t="s">
         <v>143</v>
       </c>
-      <c r="J41" s="84">
+      <c r="J41" s="79">
         <v>1</v>
       </c>
-      <c r="K41" s="73">
+      <c r="K41" s="68">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L41" s="73"/>
+      <c r="L41" s="68"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="75"/>
-      <c r="C42" s="76"/>
-      <c r="D42" s="77"/>
-      <c r="E42" s="78"/>
-      <c r="F42" s="79"/>
-      <c r="G42" s="80"/>
-      <c r="H42" s="79"/>
-      <c r="I42" s="80"/>
-      <c r="J42" s="80"/>
-      <c r="K42" s="80"/>
-      <c r="L42" s="86"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="75"/>
+      <c r="H42" s="74"/>
+      <c r="I42" s="75"/>
+      <c r="J42" s="75"/>
+      <c r="K42" s="75"/>
+      <c r="L42" s="85"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
@@ -2960,7 +2951,7 @@
       <c r="I43" s="9"/>
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
-      <c r="L43" s="87"/>
+      <c r="L43" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="3">
